--- a/data/ECN/ECN_STN_Master(SLH1).xlsx
+++ b/data/ECN/ECN_STN_Master(SLH1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\192.168.0.100\500 생산\550 국내CS\ECT&amp;STN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A833AF44-D87B-4005-89AF-401F189CE3C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFF0ED6B-964E-4FC4-91E3-0430F2A53DA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="21840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="532" uniqueCount="293">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="517" uniqueCount="284">
   <si>
     <t>날짜</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -641,13 +641,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>2026.01,02</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2026.01,09</t>
-  </si>
-  <si>
     <t>SLH1-PP-260102-01</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -659,10 +652,6 @@
     <t xml:space="preserve"> -명판 부착을 위한 탭 추가
 -전장팀 요청 버튼 조작을 위한 REAR MONITER COVER 탭 추가
 -전장팀 요청 버튼 조작을 위한 REAR MONITER COVER의 여닫이 COVER 추가</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2026.01,05</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -761,9 +750,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>2026.01,06</t>
-  </si>
-  <si>
     <t>SLH1-PP-260106-01</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -803,10 +789,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>2026.01,07</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>SLH1-PP-260107-06</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -819,10 +801,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>2026.01,13</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>SLH1-PP-260113-01</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -835,10 +813,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>2026.01,14</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>2호기</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -852,10 +826,6 @@
   </si>
   <si>
     <t>TRAY GUIDE BLOCK 길이 다르게 수정하여 TEST 진행</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2026.01,12</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1097,10 +1067,6 @@
 -브라켓 조절 시 볼트와 간섭으로 인한 형상 변경
 -미사용 센서 폐기
 -구매팀 요청 CCTV 세트화 해제로 인한 추가 발주</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2026.21.21</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -2881,7 +2847,7 @@
         <v>5</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>291</v>
+        <v>282</v>
       </c>
       <c r="F2" s="7" t="s">
         <v>14</v>
@@ -2899,7 +2865,7 @@
         <v>12</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>292</v>
+        <v>283</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.4">
@@ -2980,7 +2946,7 @@
         <v>30</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>286</v>
+        <v>277</v>
       </c>
       <c r="I5" s="11" t="s">
         <v>35</v>
@@ -3302,7 +3268,7 @@
         <v>70</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>287</v>
+        <v>278</v>
       </c>
       <c r="I17" s="11" t="s">
         <v>71</v>
@@ -3330,7 +3296,7 @@
         <v>72</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>288</v>
+        <v>279</v>
       </c>
       <c r="I18" s="11" t="s">
         <v>74</v>
@@ -3358,7 +3324,7 @@
         <v>72</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>289</v>
+        <v>280</v>
       </c>
       <c r="I19" s="11"/>
       <c r="J19" s="23"/>
@@ -3570,7 +3536,7 @@
         <v>99</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>290</v>
+        <v>281</v>
       </c>
       <c r="I27" s="11"/>
       <c r="J27" s="23"/>
@@ -3850,13 +3816,13 @@
         <v>22</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="I38" s="11"/>
       <c r="J38" s="23"/>
@@ -3917,8 +3883,8 @@
       <c r="K40" s="1"/>
     </row>
     <row r="41" spans="2:11" ht="87" x14ac:dyDescent="0.4">
-      <c r="B41" s="9" t="s">
-        <v>138</v>
+      <c r="B41" s="9">
+        <v>46024</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>4</v>
@@ -3930,47 +3896,47 @@
         <v>22</v>
       </c>
       <c r="F41" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="G41" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="H41" s="2" t="s">
         <v>140</v>
-      </c>
-      <c r="G41" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="H41" s="2" t="s">
-        <v>142</v>
       </c>
       <c r="I41" s="11"/>
       <c r="J41" s="23"/>
       <c r="K41" s="1"/>
     </row>
     <row r="42" spans="2:11" ht="34.799999999999997" x14ac:dyDescent="0.4">
-      <c r="B42" s="9" t="s">
-        <v>138</v>
+      <c r="B42" s="9">
+        <v>46024</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D42" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F42" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="G42" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="H42" s="2" t="s">
         <v>150</v>
-      </c>
-      <c r="E42" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F42" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="G42" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="H42" s="2" t="s">
-        <v>153</v>
       </c>
       <c r="I42" s="11"/>
       <c r="J42" s="23"/>
       <c r="K42" s="1"/>
     </row>
     <row r="43" spans="2:11" ht="139.19999999999999" x14ac:dyDescent="0.4">
-      <c r="B43" s="9" t="s">
-        <v>143</v>
+      <c r="B43" s="9">
+        <v>46027</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>45</v>
@@ -3982,21 +3948,21 @@
         <v>22</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="I43" s="11"/>
       <c r="J43" s="23"/>
       <c r="K43" s="1"/>
     </row>
     <row r="44" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="B44" s="9" t="s">
-        <v>143</v>
+      <c r="B44" s="9">
+        <v>46027</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>4</v>
@@ -4008,21 +3974,21 @@
         <v>22</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="I44" s="11"/>
       <c r="J44" s="23"/>
       <c r="K44" s="1"/>
     </row>
     <row r="45" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="B45" s="9" t="s">
-        <v>143</v>
+      <c r="B45" s="9">
+        <v>46027</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>4</v>
@@ -4034,23 +4000,23 @@
         <v>22</v>
       </c>
       <c r="F45" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="G45" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="H45" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="I45" s="11" t="s">
         <v>157</v>
-      </c>
-      <c r="G45" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="H45" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="I45" s="11" t="s">
-        <v>160</v>
       </c>
       <c r="J45" s="23"/>
       <c r="K45" s="1"/>
     </row>
     <row r="46" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="B46" s="9" t="s">
-        <v>143</v>
+      <c r="B46" s="9">
+        <v>46027</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>4</v>
@@ -4062,21 +4028,21 @@
         <v>22</v>
       </c>
       <c r="F46" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="G46" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="H46" s="2" t="s">
         <v>161</v>
-      </c>
-      <c r="G46" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="H46" s="2" t="s">
-        <v>164</v>
       </c>
       <c r="I46" s="11"/>
       <c r="J46" s="23"/>
       <c r="K46" s="1"/>
     </row>
     <row r="47" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="B47" s="9" t="s">
-        <v>143</v>
+      <c r="B47" s="9">
+        <v>46027</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>4</v>
@@ -4088,21 +4054,21 @@
         <v>16</v>
       </c>
       <c r="F47" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="G47" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="G47" s="1" t="s">
-        <v>165</v>
-      </c>
       <c r="H47" s="2" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="I47" s="11"/>
       <c r="J47" s="23"/>
       <c r="K47" s="1"/>
     </row>
     <row r="48" spans="2:11" ht="34.799999999999997" x14ac:dyDescent="0.4">
-      <c r="B48" s="9" t="s">
-        <v>167</v>
+      <c r="B48" s="9">
+        <v>46027</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>4</v>
@@ -4114,21 +4080,21 @@
         <v>22</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="I48" s="11"/>
       <c r="J48" s="23"/>
       <c r="K48" s="1"/>
     </row>
     <row r="49" spans="2:11" ht="34.799999999999997" x14ac:dyDescent="0.4">
-      <c r="B49" s="9" t="s">
-        <v>139</v>
+      <c r="B49" s="9">
+        <v>46031</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>45</v>
@@ -4140,21 +4106,21 @@
         <v>37</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="I49" s="11"/>
       <c r="J49" s="23"/>
       <c r="K49" s="1"/>
     </row>
     <row r="50" spans="2:11" ht="69.599999999999994" x14ac:dyDescent="0.4">
-      <c r="B50" s="9" t="s">
-        <v>139</v>
+      <c r="B50" s="9">
+        <v>46031</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>45</v>
@@ -4166,47 +4132,47 @@
         <v>22</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="I50" s="11"/>
       <c r="J50" s="23"/>
       <c r="K50" s="1"/>
     </row>
     <row r="51" spans="2:11" ht="34.799999999999997" x14ac:dyDescent="0.4">
-      <c r="B51" s="9" t="s">
-        <v>177</v>
+      <c r="B51" s="9">
+        <v>46029</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="E51" s="1" t="s">
         <v>22</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="I51" s="11"/>
       <c r="J51" s="23"/>
       <c r="K51" s="1"/>
     </row>
     <row r="52" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="B52" s="9" t="s">
-        <v>181</v>
+      <c r="B52" s="9">
+        <v>46035</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>4</v>
@@ -4218,21 +4184,21 @@
         <v>16</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="I52" s="11"/>
       <c r="J52" s="23"/>
       <c r="K52" s="1"/>
     </row>
     <row r="53" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="B53" s="9" t="s">
-        <v>185</v>
+      <c r="B53" s="9">
+        <v>46036</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>4</v>
@@ -4241,24 +4207,24 @@
         <v>112</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="I53" s="11"/>
       <c r="J53" s="23"/>
       <c r="K53" s="1"/>
     </row>
     <row r="54" spans="2:11" ht="139.19999999999999" x14ac:dyDescent="0.4">
-      <c r="B54" s="9" t="s">
-        <v>190</v>
+      <c r="B54" s="9">
+        <v>46034</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>4</v>
@@ -4270,13 +4236,13 @@
         <v>22</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>191</v>
+        <v>183</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
       <c r="I54" s="11"/>
       <c r="J54" s="23"/>
@@ -4296,13 +4262,13 @@
         <v>22</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>195</v>
+        <v>187</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="I55" s="11"/>
       <c r="J55" s="23"/>
@@ -4322,13 +4288,13 @@
         <v>22</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>199</v>
+        <v>191</v>
       </c>
       <c r="I56" s="11"/>
       <c r="J56" s="23"/>
@@ -4348,13 +4314,13 @@
         <v>22</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="I57" s="11"/>
       <c r="J57" s="23"/>
@@ -4374,13 +4340,13 @@
         <v>16</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="H58" s="1" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="I58" s="11"/>
       <c r="J58" s="23"/>
@@ -4400,21 +4366,21 @@
         <v>22</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="I59" s="11"/>
       <c r="J59" s="23"/>
       <c r="K59" s="1"/>
     </row>
     <row r="60" spans="2:11" ht="34.799999999999997" x14ac:dyDescent="0.4">
-      <c r="B60" s="9" t="s">
-        <v>243</v>
+      <c r="B60" s="9">
+        <v>46043</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>45</v>
@@ -4426,13 +4392,13 @@
         <v>22</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>245</v>
+        <v>236</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>246</v>
+        <v>237</v>
       </c>
       <c r="I60" s="11"/>
       <c r="J60" s="23"/>
@@ -4452,13 +4418,13 @@
         <v>22</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>252</v>
+        <v>243</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>253</v>
+        <v>244</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>246</v>
+        <v>237</v>
       </c>
       <c r="I61" s="11"/>
       <c r="J61" s="23"/>
@@ -4478,16 +4444,16 @@
         <v>16</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="G62" s="1" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="I62" s="11" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="J62" s="23"/>
       <c r="K62" s="1"/>
@@ -4506,13 +4472,13 @@
         <v>22</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="G63" s="1" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="H63" s="2" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="I63" s="11"/>
       <c r="J63" s="23"/>
@@ -4526,19 +4492,19 @@
         <v>4</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="E64" s="1" t="s">
         <v>16</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="G64" s="1" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="I64" s="11"/>
       <c r="J64" s="23"/>
@@ -4558,13 +4524,13 @@
         <v>22</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
       <c r="G65" s="1" t="s">
-        <v>220</v>
+        <v>212</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>221</v>
+        <v>213</v>
       </c>
       <c r="I65" s="11"/>
       <c r="J65" s="23"/>
@@ -4584,13 +4550,13 @@
         <v>22</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>222</v>
+        <v>214</v>
       </c>
       <c r="G66" s="1" t="s">
-        <v>223</v>
+        <v>215</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="I66" s="11"/>
       <c r="J66" s="23"/>
@@ -4610,13 +4576,13 @@
         <v>22</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="G67" s="1" t="s">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="H67" s="2" t="s">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="I67" s="11"/>
       <c r="J67" s="23"/>
@@ -4630,19 +4596,19 @@
         <v>4</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>285</v>
+        <v>276</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="G68" s="1" t="s">
-        <v>229</v>
+        <v>221</v>
       </c>
       <c r="H68" s="2" t="s">
-        <v>230</v>
+        <v>222</v>
       </c>
       <c r="I68" s="11"/>
       <c r="J68" s="23"/>
@@ -4656,19 +4622,19 @@
         <v>4</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>231</v>
+        <v>223</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="G69" s="1" t="s">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>233</v>
+        <v>225</v>
       </c>
       <c r="I69" s="11"/>
       <c r="J69" s="23"/>
@@ -4688,13 +4654,13 @@
         <v>22</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="G70" s="1" t="s">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="I70" s="11"/>
       <c r="J70" s="23"/>
@@ -4714,13 +4680,13 @@
         <v>22</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="G71" s="1" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="I71" s="11"/>
       <c r="J71" s="23"/>
@@ -4740,13 +4706,13 @@
         <v>22</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="G72" s="1" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="H72" s="2" t="s">
-        <v>242</v>
+        <v>234</v>
       </c>
       <c r="I72" s="11"/>
       <c r="J72" s="23"/>
@@ -4766,13 +4732,13 @@
         <v>22</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>247</v>
+        <v>238</v>
       </c>
       <c r="G73" s="1" t="s">
-        <v>248</v>
+        <v>239</v>
       </c>
       <c r="H73" s="2" t="s">
-        <v>249</v>
+        <v>240</v>
       </c>
       <c r="I73" s="11"/>
       <c r="J73" s="23"/>
@@ -4792,13 +4758,13 @@
         <v>22</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>250</v>
+        <v>241</v>
       </c>
       <c r="G74" s="1" t="s">
-        <v>251</v>
+        <v>242</v>
       </c>
       <c r="H74" s="2" t="s">
-        <v>251</v>
+        <v>242</v>
       </c>
       <c r="I74" s="11"/>
       <c r="J74" s="23"/>
@@ -4818,13 +4784,13 @@
         <v>22</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>254</v>
+        <v>245</v>
       </c>
       <c r="G75" s="1" t="s">
-        <v>255</v>
+        <v>246</v>
       </c>
       <c r="H75" s="1" t="s">
-        <v>255</v>
+        <v>246</v>
       </c>
       <c r="I75" s="11"/>
       <c r="J75" s="23"/>
@@ -4844,13 +4810,13 @@
         <v>22</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>256</v>
+        <v>247</v>
       </c>
       <c r="G76" s="1" t="s">
-        <v>257</v>
+        <v>248</v>
       </c>
       <c r="H76" s="1" t="s">
-        <v>258</v>
+        <v>249</v>
       </c>
       <c r="I76" s="11"/>
       <c r="J76" s="23"/>
@@ -4870,13 +4836,13 @@
         <v>22</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>259</v>
+        <v>250</v>
       </c>
       <c r="G77" s="1" t="s">
-        <v>245</v>
+        <v>236</v>
       </c>
       <c r="H77" s="2" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="I77" s="11"/>
       <c r="J77" s="23"/>
@@ -4896,13 +4862,13 @@
         <v>22</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>261</v>
+        <v>252</v>
       </c>
       <c r="G78" s="1" t="s">
-        <v>262</v>
+        <v>253</v>
       </c>
       <c r="H78" s="2" t="s">
-        <v>263</v>
+        <v>254</v>
       </c>
       <c r="I78" s="11"/>
       <c r="J78" s="23"/>
@@ -4916,19 +4882,19 @@
         <v>45</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>264</v>
+        <v>255</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>265</v>
+        <v>256</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>268</v>
+        <v>259</v>
       </c>
       <c r="G79" s="1" t="s">
-        <v>266</v>
+        <v>257</v>
       </c>
       <c r="H79" s="2" t="s">
-        <v>267</v>
+        <v>258</v>
       </c>
       <c r="I79" s="11"/>
       <c r="J79" s="23"/>
@@ -4948,13 +4914,13 @@
         <v>22</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>269</v>
+        <v>260</v>
       </c>
       <c r="G80" s="1" t="s">
-        <v>270</v>
+        <v>261</v>
       </c>
       <c r="H80" s="2" t="s">
-        <v>271</v>
+        <v>262</v>
       </c>
       <c r="I80" s="11"/>
       <c r="J80" s="23"/>
@@ -4974,13 +4940,13 @@
         <v>22</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>272</v>
+        <v>263</v>
       </c>
       <c r="G81" s="1" t="s">
-        <v>273</v>
+        <v>264</v>
       </c>
       <c r="H81" s="2" t="s">
-        <v>274</v>
+        <v>265</v>
       </c>
       <c r="I81" s="11"/>
       <c r="J81" s="23"/>
@@ -5000,13 +4966,13 @@
         <v>22</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>275</v>
+        <v>266</v>
       </c>
       <c r="G82" s="1" t="s">
-        <v>276</v>
+        <v>267</v>
       </c>
       <c r="H82" s="2" t="s">
-        <v>277</v>
+        <v>268</v>
       </c>
       <c r="I82" s="11"/>
       <c r="J82" s="23"/>
@@ -5020,19 +4986,19 @@
         <v>4</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>278</v>
+        <v>269</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>279</v>
+        <v>270</v>
       </c>
       <c r="G83" s="1" t="s">
-        <v>280</v>
+        <v>271</v>
       </c>
       <c r="H83" s="2" t="s">
-        <v>281</v>
+        <v>272</v>
       </c>
       <c r="I83" s="11"/>
       <c r="J83" s="23"/>
@@ -5052,13 +5018,13 @@
         <v>22</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>282</v>
+        <v>273</v>
       </c>
       <c r="G84" s="1" t="s">
-        <v>283</v>
+        <v>274</v>
       </c>
       <c r="H84" s="2" t="s">
-        <v>284</v>
+        <v>275</v>
       </c>
       <c r="I84" s="11"/>
       <c r="J84" s="23"/>

--- a/data/ECN/ECN_STN_Master(SLH1).xlsx
+++ b/data/ECN/ECN_STN_Master(SLH1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\192.168.0.100\500 생산\550 국내CS\ECT&amp;STN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFF0ED6B-964E-4FC4-91E3-0430F2A53DA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C284F91-A153-4F78-AFB0-1B39835800F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="21840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1378,7 +1378,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="16">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -1477,51 +1477,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color indexed="10"/>
       </left>
@@ -1592,26 +1547,13 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1621,7 +1563,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1651,13 +1593,13 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="2" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="2" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -1666,25 +1608,10 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2820,7 +2747,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7291A57C-081A-4156-9DDF-616C24DF1534}">
-  <dimension ref="A1:K128"/>
+  <dimension ref="A1:K84"/>
   <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="1.69921875" style="4" customWidth="1"/>
@@ -2861,7 +2788,7 @@
       <c r="I2" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="J2" s="22" t="s">
+      <c r="J2" s="18" t="s">
         <v>12</v>
       </c>
       <c r="K2" s="1" t="s">
@@ -2893,7 +2820,7 @@
       <c r="I3" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="J3" s="23" t="s">
+      <c r="J3" s="19" t="s">
         <v>13</v>
       </c>
       <c r="K3" s="1"/>
@@ -2923,7 +2850,7 @@
       <c r="I4" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="J4" s="23"/>
+      <c r="J4" s="19"/>
       <c r="K4" s="1"/>
     </row>
     <row r="5" spans="1:11" ht="276" customHeight="1" x14ac:dyDescent="0.4">
@@ -2951,7 +2878,7 @@
       <c r="I5" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="J5" s="23"/>
+      <c r="J5" s="19"/>
       <c r="K5" s="1"/>
     </row>
     <row r="6" spans="1:11" ht="87" customHeight="1" x14ac:dyDescent="0.4">
@@ -2979,7 +2906,7 @@
       <c r="I6" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="J6" s="23"/>
+      <c r="J6" s="19"/>
       <c r="K6" s="1"/>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.4">
@@ -3005,7 +2932,7 @@
       <c r="I7" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="J7" s="23"/>
+      <c r="J7" s="19"/>
       <c r="K7" s="1"/>
     </row>
     <row r="8" spans="1:11" ht="34.799999999999997" x14ac:dyDescent="0.4">
@@ -3029,7 +2956,7 @@
       </c>
       <c r="H8" s="2"/>
       <c r="I8" s="11"/>
-      <c r="J8" s="23"/>
+      <c r="J8" s="19"/>
       <c r="K8" s="1"/>
     </row>
     <row r="9" spans="1:11" ht="69.599999999999994" x14ac:dyDescent="0.4">
@@ -3055,7 +2982,7 @@
         <v>39</v>
       </c>
       <c r="I9" s="11"/>
-      <c r="J9" s="23"/>
+      <c r="J9" s="19"/>
       <c r="K9" s="1"/>
     </row>
     <row r="10" spans="1:11" ht="69.599999999999994" x14ac:dyDescent="0.4">
@@ -3083,7 +3010,7 @@
       <c r="I10" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="J10" s="23"/>
+      <c r="J10" s="19"/>
       <c r="K10" s="1"/>
     </row>
     <row r="11" spans="1:11" s="16" customFormat="1" ht="34.799999999999997" x14ac:dyDescent="0.4">
@@ -3110,8 +3037,8 @@
         <v>51</v>
       </c>
       <c r="I11" s="11"/>
-      <c r="J11" s="23"/>
-      <c r="K11" s="25"/>
+      <c r="J11" s="19"/>
+      <c r="K11" s="20"/>
     </row>
     <row r="12" spans="1:11" s="16" customFormat="1" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A12" s="13"/>
@@ -3137,8 +3064,8 @@
         <v>54</v>
       </c>
       <c r="I12" s="11"/>
-      <c r="J12" s="23"/>
-      <c r="K12" s="25"/>
+      <c r="J12" s="19"/>
+      <c r="K12" s="20"/>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.4">
       <c r="B13" s="9">
@@ -3165,7 +3092,7 @@
       <c r="I13" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="J13" s="23"/>
+      <c r="J13" s="19"/>
       <c r="K13" s="1"/>
     </row>
     <row r="14" spans="1:11" ht="121.8" x14ac:dyDescent="0.4">
@@ -3193,7 +3120,7 @@
       <c r="I14" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="J14" s="23"/>
+      <c r="J14" s="19"/>
       <c r="K14" s="1"/>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.4">
@@ -3219,7 +3146,7 @@
         <v>65</v>
       </c>
       <c r="I15" s="11"/>
-      <c r="J15" s="23"/>
+      <c r="J15" s="19"/>
       <c r="K15" s="1"/>
     </row>
     <row r="16" spans="1:11" ht="40.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
@@ -3245,7 +3172,7 @@
         <v>68</v>
       </c>
       <c r="I16" s="11"/>
-      <c r="J16" s="23"/>
+      <c r="J16" s="19"/>
       <c r="K16" s="1"/>
     </row>
     <row r="17" spans="2:11" ht="156" customHeight="1" x14ac:dyDescent="0.4">
@@ -3273,7 +3200,7 @@
       <c r="I17" s="11" t="s">
         <v>71</v>
       </c>
-      <c r="J17" s="23"/>
+      <c r="J17" s="19"/>
       <c r="K17" s="1"/>
     </row>
     <row r="18" spans="2:11" ht="135" customHeight="1" x14ac:dyDescent="0.4">
@@ -3301,7 +3228,7 @@
       <c r="I18" s="11" t="s">
         <v>74</v>
       </c>
-      <c r="J18" s="23"/>
+      <c r="J18" s="19"/>
       <c r="K18" s="1"/>
     </row>
     <row r="19" spans="2:11" ht="180" customHeight="1" x14ac:dyDescent="0.4">
@@ -3327,7 +3254,7 @@
         <v>280</v>
       </c>
       <c r="I19" s="11"/>
-      <c r="J19" s="23"/>
+      <c r="J19" s="19"/>
       <c r="K19" s="1"/>
     </row>
     <row r="20" spans="2:11" ht="121.8" x14ac:dyDescent="0.4">
@@ -3355,7 +3282,7 @@
       <c r="I20" s="11" t="s">
         <v>82</v>
       </c>
-      <c r="J20" s="23"/>
+      <c r="J20" s="19"/>
       <c r="K20" s="1"/>
     </row>
     <row r="21" spans="2:11" ht="87" x14ac:dyDescent="0.4">
@@ -3383,7 +3310,7 @@
       <c r="I21" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="J21" s="23"/>
+      <c r="J21" s="19"/>
       <c r="K21" s="1"/>
     </row>
     <row r="22" spans="2:11" ht="128.4" customHeight="1" x14ac:dyDescent="0.4">
@@ -3409,7 +3336,7 @@
         <v>85</v>
       </c>
       <c r="I22" s="11"/>
-      <c r="J22" s="23"/>
+      <c r="J22" s="19"/>
       <c r="K22" s="1"/>
     </row>
     <row r="23" spans="2:11" ht="87" x14ac:dyDescent="0.4">
@@ -3435,7 +3362,7 @@
         <v>88</v>
       </c>
       <c r="I23" s="11"/>
-      <c r="J23" s="23"/>
+      <c r="J23" s="19"/>
       <c r="K23" s="1"/>
     </row>
     <row r="24" spans="2:11" ht="52.2" x14ac:dyDescent="0.4">
@@ -3461,7 +3388,7 @@
         <v>91</v>
       </c>
       <c r="I24" s="11"/>
-      <c r="J24" s="23"/>
+      <c r="J24" s="19"/>
       <c r="K24" s="1"/>
     </row>
     <row r="25" spans="2:11" ht="69.599999999999994" x14ac:dyDescent="0.4">
@@ -3487,7 +3414,7 @@
         <v>94</v>
       </c>
       <c r="I25" s="11"/>
-      <c r="J25" s="23"/>
+      <c r="J25" s="19"/>
       <c r="K25" s="1"/>
     </row>
     <row r="26" spans="2:11" ht="104.4" x14ac:dyDescent="0.4">
@@ -3513,7 +3440,7 @@
         <v>97</v>
       </c>
       <c r="I26" s="11"/>
-      <c r="J26" s="23"/>
+      <c r="J26" s="19"/>
       <c r="K26" s="1"/>
     </row>
     <row r="27" spans="2:11" ht="190.8" customHeight="1" x14ac:dyDescent="0.4">
@@ -3539,7 +3466,7 @@
         <v>281</v>
       </c>
       <c r="I27" s="11"/>
-      <c r="J27" s="23"/>
+      <c r="J27" s="19"/>
       <c r="K27" s="1"/>
     </row>
     <row r="28" spans="2:11" ht="52.2" x14ac:dyDescent="0.4">
@@ -3565,7 +3492,7 @@
         <v>102</v>
       </c>
       <c r="I28" s="11"/>
-      <c r="J28" s="23"/>
+      <c r="J28" s="19"/>
       <c r="K28" s="1"/>
     </row>
     <row r="29" spans="2:11" x14ac:dyDescent="0.4">
@@ -3591,7 +3518,7 @@
         <v>105</v>
       </c>
       <c r="I29" s="11"/>
-      <c r="J29" s="23"/>
+      <c r="J29" s="19"/>
       <c r="K29" s="1"/>
     </row>
     <row r="30" spans="2:11" x14ac:dyDescent="0.4">
@@ -3617,7 +3544,7 @@
         <v>108</v>
       </c>
       <c r="I30" s="11"/>
-      <c r="J30" s="23"/>
+      <c r="J30" s="19"/>
       <c r="K30" s="1"/>
     </row>
     <row r="31" spans="2:11" ht="87" x14ac:dyDescent="0.4">
@@ -3643,7 +3570,7 @@
         <v>111</v>
       </c>
       <c r="I31" s="11"/>
-      <c r="J31" s="23"/>
+      <c r="J31" s="19"/>
       <c r="K31" s="1"/>
     </row>
     <row r="32" spans="2:11" x14ac:dyDescent="0.4">
@@ -3669,7 +3596,7 @@
         <v>115</v>
       </c>
       <c r="I32" s="11"/>
-      <c r="J32" s="23"/>
+      <c r="J32" s="19"/>
       <c r="K32" s="1"/>
     </row>
     <row r="33" spans="2:11" ht="69.599999999999994" x14ac:dyDescent="0.4">
@@ -3695,7 +3622,7 @@
         <v>118</v>
       </c>
       <c r="I33" s="11"/>
-      <c r="J33" s="23"/>
+      <c r="J33" s="19"/>
       <c r="K33" s="1"/>
     </row>
     <row r="34" spans="2:11" ht="34.799999999999997" x14ac:dyDescent="0.4">
@@ -3721,7 +3648,7 @@
         <v>121</v>
       </c>
       <c r="I34" s="11"/>
-      <c r="J34" s="23"/>
+      <c r="J34" s="19"/>
       <c r="K34" s="1"/>
     </row>
     <row r="35" spans="2:11" ht="226.2" x14ac:dyDescent="0.4">
@@ -3747,7 +3674,7 @@
         <v>124</v>
       </c>
       <c r="I35" s="11"/>
-      <c r="J35" s="23"/>
+      <c r="J35" s="19"/>
       <c r="K35" s="1"/>
     </row>
     <row r="36" spans="2:11" ht="87" x14ac:dyDescent="0.4">
@@ -3773,7 +3700,7 @@
         <v>130</v>
       </c>
       <c r="I36" s="11"/>
-      <c r="J36" s="23"/>
+      <c r="J36" s="19"/>
       <c r="K36" s="1"/>
     </row>
     <row r="37" spans="2:11" ht="69.599999999999994" x14ac:dyDescent="0.4">
@@ -3799,7 +3726,7 @@
         <v>127</v>
       </c>
       <c r="I37" s="11"/>
-      <c r="J37" s="23"/>
+      <c r="J37" s="19"/>
       <c r="K37" s="1"/>
     </row>
     <row r="38" spans="2:11" ht="69.599999999999994" x14ac:dyDescent="0.4">
@@ -3825,7 +3752,7 @@
         <v>146</v>
       </c>
       <c r="I38" s="11"/>
-      <c r="J38" s="23"/>
+      <c r="J38" s="19"/>
       <c r="K38" s="1"/>
     </row>
     <row r="39" spans="2:11" ht="104.4" x14ac:dyDescent="0.4">
@@ -3851,7 +3778,7 @@
         <v>133</v>
       </c>
       <c r="I39" s="11"/>
-      <c r="J39" s="23"/>
+      <c r="J39" s="19"/>
       <c r="K39" s="1"/>
     </row>
     <row r="40" spans="2:11" ht="139.19999999999999" x14ac:dyDescent="0.4">
@@ -3879,7 +3806,7 @@
       <c r="I40" s="11" t="s">
         <v>137</v>
       </c>
-      <c r="J40" s="23"/>
+      <c r="J40" s="19"/>
       <c r="K40" s="1"/>
     </row>
     <row r="41" spans="2:11" ht="87" x14ac:dyDescent="0.4">
@@ -3905,7 +3832,7 @@
         <v>140</v>
       </c>
       <c r="I41" s="11"/>
-      <c r="J41" s="23"/>
+      <c r="J41" s="19"/>
       <c r="K41" s="1"/>
     </row>
     <row r="42" spans="2:11" ht="34.799999999999997" x14ac:dyDescent="0.4">
@@ -3931,7 +3858,7 @@
         <v>150</v>
       </c>
       <c r="I42" s="11"/>
-      <c r="J42" s="23"/>
+      <c r="J42" s="19"/>
       <c r="K42" s="1"/>
     </row>
     <row r="43" spans="2:11" ht="139.19999999999999" x14ac:dyDescent="0.4">
@@ -3957,7 +3884,7 @@
         <v>143</v>
       </c>
       <c r="I43" s="11"/>
-      <c r="J43" s="23"/>
+      <c r="J43" s="19"/>
       <c r="K43" s="1"/>
     </row>
     <row r="44" spans="2:11" x14ac:dyDescent="0.4">
@@ -3983,7 +3910,7 @@
         <v>153</v>
       </c>
       <c r="I44" s="11"/>
-      <c r="J44" s="23"/>
+      <c r="J44" s="19"/>
       <c r="K44" s="1"/>
     </row>
     <row r="45" spans="2:11" x14ac:dyDescent="0.4">
@@ -4011,7 +3938,7 @@
       <c r="I45" s="11" t="s">
         <v>157</v>
       </c>
-      <c r="J45" s="23"/>
+      <c r="J45" s="19"/>
       <c r="K45" s="1"/>
     </row>
     <row r="46" spans="2:11" x14ac:dyDescent="0.4">
@@ -4037,7 +3964,7 @@
         <v>161</v>
       </c>
       <c r="I46" s="11"/>
-      <c r="J46" s="23"/>
+      <c r="J46" s="19"/>
       <c r="K46" s="1"/>
     </row>
     <row r="47" spans="2:11" x14ac:dyDescent="0.4">
@@ -4063,7 +3990,7 @@
         <v>163</v>
       </c>
       <c r="I47" s="11"/>
-      <c r="J47" s="23"/>
+      <c r="J47" s="19"/>
       <c r="K47" s="1"/>
     </row>
     <row r="48" spans="2:11" ht="34.799999999999997" x14ac:dyDescent="0.4">
@@ -4089,7 +4016,7 @@
         <v>165</v>
       </c>
       <c r="I48" s="11"/>
-      <c r="J48" s="23"/>
+      <c r="J48" s="19"/>
       <c r="K48" s="1"/>
     </row>
     <row r="49" spans="2:11" ht="34.799999999999997" x14ac:dyDescent="0.4">
@@ -4115,7 +4042,7 @@
         <v>169</v>
       </c>
       <c r="I49" s="11"/>
-      <c r="J49" s="23"/>
+      <c r="J49" s="19"/>
       <c r="K49" s="1"/>
     </row>
     <row r="50" spans="2:11" ht="69.599999999999994" x14ac:dyDescent="0.4">
@@ -4141,7 +4068,7 @@
         <v>172</v>
       </c>
       <c r="I50" s="11"/>
-      <c r="J50" s="23"/>
+      <c r="J50" s="19"/>
       <c r="K50" s="1"/>
     </row>
     <row r="51" spans="2:11" ht="34.799999999999997" x14ac:dyDescent="0.4">
@@ -4167,7 +4094,7 @@
         <v>175</v>
       </c>
       <c r="I51" s="11"/>
-      <c r="J51" s="23"/>
+      <c r="J51" s="19"/>
       <c r="K51" s="1"/>
     </row>
     <row r="52" spans="2:11" x14ac:dyDescent="0.4">
@@ -4193,7 +4120,7 @@
         <v>178</v>
       </c>
       <c r="I52" s="11"/>
-      <c r="J52" s="23"/>
+      <c r="J52" s="19"/>
       <c r="K52" s="1"/>
     </row>
     <row r="53" spans="2:11" x14ac:dyDescent="0.4">
@@ -4219,7 +4146,7 @@
         <v>182</v>
       </c>
       <c r="I53" s="11"/>
-      <c r="J53" s="23"/>
+      <c r="J53" s="19"/>
       <c r="K53" s="1"/>
     </row>
     <row r="54" spans="2:11" ht="139.19999999999999" x14ac:dyDescent="0.4">
@@ -4245,7 +4172,7 @@
         <v>185</v>
       </c>
       <c r="I54" s="11"/>
-      <c r="J54" s="23"/>
+      <c r="J54" s="19"/>
       <c r="K54" s="1"/>
     </row>
     <row r="55" spans="2:11" ht="52.2" x14ac:dyDescent="0.4">
@@ -4271,7 +4198,7 @@
         <v>188</v>
       </c>
       <c r="I55" s="11"/>
-      <c r="J55" s="23"/>
+      <c r="J55" s="19"/>
       <c r="K55" s="1"/>
     </row>
     <row r="56" spans="2:11" ht="34.799999999999997" x14ac:dyDescent="0.4">
@@ -4297,7 +4224,7 @@
         <v>191</v>
       </c>
       <c r="I56" s="11"/>
-      <c r="J56" s="23"/>
+      <c r="J56" s="19"/>
       <c r="K56" s="1"/>
     </row>
     <row r="57" spans="2:11" ht="52.2" x14ac:dyDescent="0.4">
@@ -4323,7 +4250,7 @@
         <v>194</v>
       </c>
       <c r="I57" s="11"/>
-      <c r="J57" s="23"/>
+      <c r="J57" s="19"/>
       <c r="K57" s="1"/>
     </row>
     <row r="58" spans="2:11" ht="34.799999999999997" x14ac:dyDescent="0.4">
@@ -4349,7 +4276,7 @@
         <v>196</v>
       </c>
       <c r="I58" s="11"/>
-      <c r="J58" s="23"/>
+      <c r="J58" s="19"/>
       <c r="K58" s="1"/>
     </row>
     <row r="59" spans="2:11" ht="87" x14ac:dyDescent="0.4">
@@ -4375,7 +4302,7 @@
         <v>199</v>
       </c>
       <c r="I59" s="11"/>
-      <c r="J59" s="23"/>
+      <c r="J59" s="19"/>
       <c r="K59" s="1"/>
     </row>
     <row r="60" spans="2:11" ht="34.799999999999997" x14ac:dyDescent="0.4">
@@ -4401,7 +4328,7 @@
         <v>237</v>
       </c>
       <c r="I60" s="11"/>
-      <c r="J60" s="23"/>
+      <c r="J60" s="19"/>
       <c r="K60" s="1"/>
     </row>
     <row r="61" spans="2:11" ht="34.799999999999997" x14ac:dyDescent="0.4">
@@ -4427,7 +4354,7 @@
         <v>237</v>
       </c>
       <c r="I61" s="11"/>
-      <c r="J61" s="23"/>
+      <c r="J61" s="19"/>
       <c r="K61" s="1"/>
     </row>
     <row r="62" spans="2:11" x14ac:dyDescent="0.4">
@@ -4455,7 +4382,7 @@
       <c r="I62" s="11" t="s">
         <v>203</v>
       </c>
-      <c r="J62" s="23"/>
+      <c r="J62" s="19"/>
       <c r="K62" s="1"/>
     </row>
     <row r="63" spans="2:11" ht="34.799999999999997" x14ac:dyDescent="0.4">
@@ -4481,7 +4408,7 @@
         <v>206</v>
       </c>
       <c r="I63" s="11"/>
-      <c r="J63" s="23"/>
+      <c r="J63" s="19"/>
       <c r="K63" s="1"/>
     </row>
     <row r="64" spans="2:11" ht="34.799999999999997" x14ac:dyDescent="0.4">
@@ -4507,7 +4434,7 @@
         <v>210</v>
       </c>
       <c r="I64" s="11"/>
-      <c r="J64" s="23"/>
+      <c r="J64" s="19"/>
       <c r="K64" s="1"/>
     </row>
     <row r="65" spans="2:11" ht="69.599999999999994" x14ac:dyDescent="0.4">
@@ -4533,7 +4460,7 @@
         <v>213</v>
       </c>
       <c r="I65" s="11"/>
-      <c r="J65" s="23"/>
+      <c r="J65" s="19"/>
       <c r="K65" s="1"/>
     </row>
     <row r="66" spans="2:11" ht="52.2" x14ac:dyDescent="0.4">
@@ -4559,7 +4486,7 @@
         <v>216</v>
       </c>
       <c r="I66" s="11"/>
-      <c r="J66" s="23"/>
+      <c r="J66" s="19"/>
       <c r="K66" s="1"/>
     </row>
     <row r="67" spans="2:11" ht="34.799999999999997" x14ac:dyDescent="0.4">
@@ -4585,7 +4512,7 @@
         <v>219</v>
       </c>
       <c r="I67" s="11"/>
-      <c r="J67" s="23"/>
+      <c r="J67" s="19"/>
       <c r="K67" s="1"/>
     </row>
     <row r="68" spans="2:11" ht="69.599999999999994" x14ac:dyDescent="0.4">
@@ -4611,7 +4538,7 @@
         <v>222</v>
       </c>
       <c r="I68" s="11"/>
-      <c r="J68" s="23"/>
+      <c r="J68" s="19"/>
       <c r="K68" s="1"/>
     </row>
     <row r="69" spans="2:11" ht="156.6" x14ac:dyDescent="0.4">
@@ -4637,7 +4564,7 @@
         <v>225</v>
       </c>
       <c r="I69" s="11"/>
-      <c r="J69" s="23"/>
+      <c r="J69" s="19"/>
       <c r="K69" s="1"/>
     </row>
     <row r="70" spans="2:11" ht="52.2" x14ac:dyDescent="0.4">
@@ -4663,7 +4590,7 @@
         <v>228</v>
       </c>
       <c r="I70" s="11"/>
-      <c r="J70" s="23"/>
+      <c r="J70" s="19"/>
       <c r="K70" s="1"/>
     </row>
     <row r="71" spans="2:11" ht="87" x14ac:dyDescent="0.4">
@@ -4689,7 +4616,7 @@
         <v>231</v>
       </c>
       <c r="I71" s="11"/>
-      <c r="J71" s="23"/>
+      <c r="J71" s="19"/>
       <c r="K71" s="1"/>
     </row>
     <row r="72" spans="2:11" ht="139.19999999999999" x14ac:dyDescent="0.4">
@@ -4715,7 +4642,7 @@
         <v>234</v>
       </c>
       <c r="I72" s="11"/>
-      <c r="J72" s="23"/>
+      <c r="J72" s="19"/>
       <c r="K72" s="1"/>
     </row>
     <row r="73" spans="2:11" ht="139.19999999999999" x14ac:dyDescent="0.4">
@@ -4741,7 +4668,7 @@
         <v>240</v>
       </c>
       <c r="I73" s="11"/>
-      <c r="J73" s="23"/>
+      <c r="J73" s="19"/>
       <c r="K73" s="1"/>
     </row>
     <row r="74" spans="2:11" x14ac:dyDescent="0.4">
@@ -4767,7 +4694,7 @@
         <v>242</v>
       </c>
       <c r="I74" s="11"/>
-      <c r="J74" s="23"/>
+      <c r="J74" s="19"/>
       <c r="K74" s="1"/>
     </row>
     <row r="75" spans="2:11" x14ac:dyDescent="0.4">
@@ -4793,7 +4720,7 @@
         <v>246</v>
       </c>
       <c r="I75" s="11"/>
-      <c r="J75" s="23"/>
+      <c r="J75" s="19"/>
       <c r="K75" s="1"/>
     </row>
     <row r="76" spans="2:11" x14ac:dyDescent="0.4">
@@ -4819,7 +4746,7 @@
         <v>249</v>
       </c>
       <c r="I76" s="11"/>
-      <c r="J76" s="23"/>
+      <c r="J76" s="19"/>
       <c r="K76" s="1"/>
     </row>
     <row r="77" spans="2:11" ht="34.799999999999997" x14ac:dyDescent="0.4">
@@ -4845,7 +4772,7 @@
         <v>251</v>
       </c>
       <c r="I77" s="11"/>
-      <c r="J77" s="23"/>
+      <c r="J77" s="19"/>
       <c r="K77" s="1"/>
     </row>
     <row r="78" spans="2:11" ht="156.6" x14ac:dyDescent="0.4">
@@ -4871,7 +4798,7 @@
         <v>254</v>
       </c>
       <c r="I78" s="11"/>
-      <c r="J78" s="23"/>
+      <c r="J78" s="19"/>
       <c r="K78" s="1"/>
     </row>
     <row r="79" spans="2:11" ht="52.2" x14ac:dyDescent="0.4">
@@ -4897,7 +4824,7 @@
         <v>258</v>
       </c>
       <c r="I79" s="11"/>
-      <c r="J79" s="23"/>
+      <c r="J79" s="19"/>
       <c r="K79" s="1"/>
     </row>
     <row r="80" spans="2:11" ht="52.2" x14ac:dyDescent="0.4">
@@ -4923,7 +4850,7 @@
         <v>262</v>
       </c>
       <c r="I80" s="11"/>
-      <c r="J80" s="23"/>
+      <c r="J80" s="19"/>
       <c r="K80" s="1"/>
     </row>
     <row r="81" spans="2:11" ht="104.4" x14ac:dyDescent="0.4">
@@ -4949,7 +4876,7 @@
         <v>265</v>
       </c>
       <c r="I81" s="11"/>
-      <c r="J81" s="23"/>
+      <c r="J81" s="19"/>
       <c r="K81" s="1"/>
     </row>
     <row r="82" spans="2:11" ht="243.6" x14ac:dyDescent="0.4">
@@ -4975,7 +4902,7 @@
         <v>268</v>
       </c>
       <c r="I82" s="11"/>
-      <c r="J82" s="23"/>
+      <c r="J82" s="19"/>
       <c r="K82" s="1"/>
     </row>
     <row r="83" spans="2:11" ht="104.4" x14ac:dyDescent="0.4">
@@ -5001,7 +4928,7 @@
         <v>272</v>
       </c>
       <c r="I83" s="11"/>
-      <c r="J83" s="23"/>
+      <c r="J83" s="19"/>
       <c r="K83" s="1"/>
     </row>
     <row r="84" spans="2:11" ht="69.599999999999994" x14ac:dyDescent="0.4">
@@ -5027,624 +4954,8 @@
         <v>275</v>
       </c>
       <c r="I84" s="11"/>
-      <c r="J84" s="23"/>
+      <c r="J84" s="19"/>
       <c r="K84" s="1"/>
-    </row>
-    <row r="85" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="B85" s="9">
-        <v>46089</v>
-      </c>
-      <c r="C85" s="1"/>
-      <c r="D85" s="1"/>
-      <c r="E85" s="1"/>
-      <c r="F85" s="1"/>
-      <c r="G85" s="1"/>
-      <c r="H85" s="2"/>
-      <c r="I85" s="11"/>
-      <c r="J85" s="23"/>
-      <c r="K85" s="1"/>
-    </row>
-    <row r="86" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="B86" s="9">
-        <v>46090</v>
-      </c>
-      <c r="C86" s="1"/>
-      <c r="D86" s="1"/>
-      <c r="E86" s="1"/>
-      <c r="F86" s="1"/>
-      <c r="G86" s="1"/>
-      <c r="H86" s="2"/>
-      <c r="I86" s="11"/>
-      <c r="J86" s="23"/>
-      <c r="K86" s="1"/>
-    </row>
-    <row r="87" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="B87" s="9">
-        <v>46091</v>
-      </c>
-      <c r="C87" s="1"/>
-      <c r="D87" s="1"/>
-      <c r="E87" s="1"/>
-      <c r="F87" s="1"/>
-      <c r="G87" s="1"/>
-      <c r="H87" s="2"/>
-      <c r="I87" s="11"/>
-      <c r="J87" s="23"/>
-      <c r="K87" s="1"/>
-    </row>
-    <row r="88" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="B88" s="9">
-        <v>46092</v>
-      </c>
-      <c r="C88" s="1"/>
-      <c r="D88" s="1"/>
-      <c r="E88" s="1"/>
-      <c r="F88" s="1"/>
-      <c r="G88" s="1"/>
-      <c r="H88" s="2"/>
-      <c r="I88" s="11"/>
-      <c r="J88" s="23"/>
-      <c r="K88" s="1"/>
-    </row>
-    <row r="89" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="B89" s="9">
-        <v>46093</v>
-      </c>
-      <c r="C89" s="1"/>
-      <c r="D89" s="1"/>
-      <c r="E89" s="1"/>
-      <c r="F89" s="1"/>
-      <c r="G89" s="1"/>
-      <c r="H89" s="2"/>
-      <c r="I89" s="11"/>
-      <c r="J89" s="23"/>
-      <c r="K89" s="1"/>
-    </row>
-    <row r="90" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="B90" s="9">
-        <v>46094</v>
-      </c>
-      <c r="C90" s="1"/>
-      <c r="D90" s="1"/>
-      <c r="E90" s="1"/>
-      <c r="F90" s="1"/>
-      <c r="G90" s="1"/>
-      <c r="H90" s="2"/>
-      <c r="I90" s="11"/>
-      <c r="J90" s="23"/>
-      <c r="K90" s="1"/>
-    </row>
-    <row r="91" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="B91" s="9">
-        <v>46095</v>
-      </c>
-      <c r="C91" s="1"/>
-      <c r="D91" s="1"/>
-      <c r="E91" s="1"/>
-      <c r="F91" s="1"/>
-      <c r="G91" s="1"/>
-      <c r="H91" s="2"/>
-      <c r="I91" s="11"/>
-      <c r="J91" s="23"/>
-      <c r="K91" s="1"/>
-    </row>
-    <row r="92" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="B92" s="9">
-        <v>46096</v>
-      </c>
-      <c r="C92" s="1"/>
-      <c r="D92" s="1"/>
-      <c r="E92" s="1"/>
-      <c r="F92" s="1"/>
-      <c r="G92" s="1"/>
-      <c r="H92" s="2"/>
-      <c r="I92" s="11"/>
-      <c r="J92" s="23"/>
-      <c r="K92" s="1"/>
-    </row>
-    <row r="93" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="B93" s="9">
-        <v>46097</v>
-      </c>
-      <c r="C93" s="1"/>
-      <c r="D93" s="1"/>
-      <c r="E93" s="1"/>
-      <c r="F93" s="1"/>
-      <c r="G93" s="1"/>
-      <c r="H93" s="2"/>
-      <c r="I93" s="11"/>
-      <c r="J93" s="23"/>
-      <c r="K93" s="1"/>
-    </row>
-    <row r="94" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="B94" s="9">
-        <v>46098</v>
-      </c>
-      <c r="C94" s="1"/>
-      <c r="D94" s="1"/>
-      <c r="E94" s="1"/>
-      <c r="F94" s="1"/>
-      <c r="G94" s="1"/>
-      <c r="H94" s="2"/>
-      <c r="I94" s="11"/>
-      <c r="J94" s="23"/>
-      <c r="K94" s="1"/>
-    </row>
-    <row r="95" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="B95" s="9">
-        <v>46099</v>
-      </c>
-      <c r="C95" s="1"/>
-      <c r="D95" s="1"/>
-      <c r="E95" s="1"/>
-      <c r="F95" s="1"/>
-      <c r="G95" s="1"/>
-      <c r="H95" s="2"/>
-      <c r="I95" s="11"/>
-      <c r="J95" s="23"/>
-      <c r="K95" s="1"/>
-    </row>
-    <row r="96" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="B96" s="9">
-        <v>46100</v>
-      </c>
-      <c r="C96" s="1"/>
-      <c r="D96" s="1"/>
-      <c r="E96" s="1"/>
-      <c r="F96" s="1"/>
-      <c r="G96" s="1"/>
-      <c r="H96" s="2"/>
-      <c r="I96" s="11"/>
-      <c r="J96" s="23"/>
-      <c r="K96" s="1"/>
-    </row>
-    <row r="97" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="B97" s="9">
-        <v>46101</v>
-      </c>
-      <c r="C97" s="1"/>
-      <c r="D97" s="1"/>
-      <c r="E97" s="1"/>
-      <c r="F97" s="1"/>
-      <c r="G97" s="1"/>
-      <c r="H97" s="2"/>
-      <c r="I97" s="11"/>
-      <c r="J97" s="23"/>
-      <c r="K97" s="1"/>
-    </row>
-    <row r="98" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="B98" s="9">
-        <v>46102</v>
-      </c>
-      <c r="C98" s="1"/>
-      <c r="D98" s="1"/>
-      <c r="E98" s="1"/>
-      <c r="F98" s="1"/>
-      <c r="G98" s="1"/>
-      <c r="H98" s="2"/>
-      <c r="I98" s="11"/>
-      <c r="J98" s="23"/>
-      <c r="K98" s="1"/>
-    </row>
-    <row r="99" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="B99" s="9">
-        <v>46103</v>
-      </c>
-      <c r="C99" s="1"/>
-      <c r="D99" s="1"/>
-      <c r="E99" s="1"/>
-      <c r="F99" s="1"/>
-      <c r="G99" s="1"/>
-      <c r="H99" s="2"/>
-      <c r="I99" s="11"/>
-      <c r="J99" s="23"/>
-      <c r="K99" s="1"/>
-    </row>
-    <row r="100" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="B100" s="9">
-        <v>46104</v>
-      </c>
-      <c r="C100" s="1"/>
-      <c r="D100" s="1"/>
-      <c r="E100" s="1"/>
-      <c r="F100" s="1"/>
-      <c r="G100" s="1"/>
-      <c r="H100" s="2"/>
-      <c r="I100" s="11"/>
-      <c r="J100" s="23"/>
-      <c r="K100" s="1"/>
-    </row>
-    <row r="101" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="B101" s="9">
-        <v>46105</v>
-      </c>
-      <c r="C101" s="1"/>
-      <c r="D101" s="1"/>
-      <c r="E101" s="1"/>
-      <c r="F101" s="1"/>
-      <c r="G101" s="1"/>
-      <c r="H101" s="2"/>
-      <c r="I101" s="11"/>
-      <c r="J101" s="23"/>
-      <c r="K101" s="1"/>
-    </row>
-    <row r="102" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="B102" s="9">
-        <v>46106</v>
-      </c>
-      <c r="C102" s="1"/>
-      <c r="D102" s="1"/>
-      <c r="E102" s="1"/>
-      <c r="F102" s="1"/>
-      <c r="G102" s="1"/>
-      <c r="H102" s="2"/>
-      <c r="I102" s="11"/>
-      <c r="J102" s="23"/>
-      <c r="K102" s="1"/>
-    </row>
-    <row r="103" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="B103" s="9">
-        <v>46107</v>
-      </c>
-      <c r="C103" s="1"/>
-      <c r="D103" s="1"/>
-      <c r="E103" s="1"/>
-      <c r="F103" s="1"/>
-      <c r="G103" s="1"/>
-      <c r="H103" s="2"/>
-      <c r="I103" s="11"/>
-      <c r="J103" s="23"/>
-      <c r="K103" s="1"/>
-    </row>
-    <row r="104" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="B104" s="9">
-        <v>46108</v>
-      </c>
-      <c r="C104" s="1"/>
-      <c r="D104" s="1"/>
-      <c r="E104" s="1"/>
-      <c r="F104" s="1"/>
-      <c r="G104" s="1"/>
-      <c r="H104" s="2"/>
-      <c r="I104" s="11"/>
-      <c r="J104" s="23"/>
-      <c r="K104" s="1"/>
-    </row>
-    <row r="105" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="B105" s="9">
-        <v>46109</v>
-      </c>
-      <c r="C105" s="1"/>
-      <c r="D105" s="1"/>
-      <c r="E105" s="1"/>
-      <c r="F105" s="1"/>
-      <c r="G105" s="1"/>
-      <c r="H105" s="2"/>
-      <c r="I105" s="11"/>
-      <c r="J105" s="23"/>
-      <c r="K105" s="1"/>
-    </row>
-    <row r="106" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="B106" s="9">
-        <v>46110</v>
-      </c>
-      <c r="C106" s="1"/>
-      <c r="D106" s="1"/>
-      <c r="E106" s="1"/>
-      <c r="F106" s="1"/>
-      <c r="G106" s="1"/>
-      <c r="H106" s="2"/>
-      <c r="I106" s="11"/>
-      <c r="J106" s="23"/>
-      <c r="K106" s="1"/>
-    </row>
-    <row r="107" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="B107" s="9">
-        <v>46111</v>
-      </c>
-      <c r="C107" s="1"/>
-      <c r="D107" s="1"/>
-      <c r="E107" s="1"/>
-      <c r="F107" s="1"/>
-      <c r="G107" s="1"/>
-      <c r="H107" s="2"/>
-      <c r="I107" s="11"/>
-      <c r="J107" s="23"/>
-      <c r="K107" s="1"/>
-    </row>
-    <row r="108" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="B108" s="9">
-        <v>46112</v>
-      </c>
-      <c r="C108" s="1"/>
-      <c r="D108" s="1"/>
-      <c r="E108" s="1"/>
-      <c r="F108" s="1"/>
-      <c r="G108" s="1"/>
-      <c r="H108" s="2"/>
-      <c r="I108" s="11"/>
-      <c r="J108" s="23"/>
-      <c r="K108" s="1"/>
-    </row>
-    <row r="109" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="B109" s="9">
-        <v>46082</v>
-      </c>
-      <c r="C109" s="1"/>
-      <c r="D109" s="1"/>
-      <c r="E109" s="1"/>
-      <c r="F109" s="1"/>
-      <c r="G109" s="1"/>
-      <c r="H109" s="2"/>
-      <c r="I109" s="11"/>
-      <c r="J109" s="23"/>
-      <c r="K109" s="1"/>
-    </row>
-    <row r="110" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="B110" s="9">
-        <v>46083</v>
-      </c>
-      <c r="C110" s="1"/>
-      <c r="D110" s="1"/>
-      <c r="E110" s="1"/>
-      <c r="F110" s="1"/>
-      <c r="G110" s="1"/>
-      <c r="H110" s="2"/>
-      <c r="I110" s="11"/>
-      <c r="J110" s="23"/>
-      <c r="K110" s="1"/>
-    </row>
-    <row r="111" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="B111" s="9">
-        <v>46084</v>
-      </c>
-      <c r="C111" s="1"/>
-      <c r="D111" s="1"/>
-      <c r="E111" s="1"/>
-      <c r="F111" s="1"/>
-      <c r="G111" s="1"/>
-      <c r="H111" s="2"/>
-      <c r="I111" s="11"/>
-      <c r="J111" s="23"/>
-      <c r="K111" s="1"/>
-    </row>
-    <row r="112" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="B112" s="9">
-        <v>46085</v>
-      </c>
-      <c r="C112" s="1"/>
-      <c r="D112" s="1"/>
-      <c r="E112" s="1"/>
-      <c r="F112" s="1"/>
-      <c r="G112" s="1"/>
-      <c r="H112" s="2"/>
-      <c r="I112" s="11"/>
-      <c r="J112" s="23"/>
-      <c r="K112" s="1"/>
-    </row>
-    <row r="113" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="B113" s="9">
-        <v>46086</v>
-      </c>
-      <c r="C113" s="1"/>
-      <c r="D113" s="1"/>
-      <c r="E113" s="1"/>
-      <c r="F113" s="1"/>
-      <c r="G113" s="1"/>
-      <c r="H113" s="2"/>
-      <c r="I113" s="11"/>
-      <c r="J113" s="23"/>
-      <c r="K113" s="1"/>
-    </row>
-    <row r="114" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="B114" s="9">
-        <v>46087</v>
-      </c>
-      <c r="C114" s="1"/>
-      <c r="D114" s="1"/>
-      <c r="E114" s="1"/>
-      <c r="F114" s="1"/>
-      <c r="G114" s="1"/>
-      <c r="H114" s="2"/>
-      <c r="I114" s="11"/>
-      <c r="J114" s="23"/>
-      <c r="K114" s="1"/>
-    </row>
-    <row r="115" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="B115" s="9">
-        <v>46088</v>
-      </c>
-      <c r="C115" s="1"/>
-      <c r="D115" s="1"/>
-      <c r="E115" s="1"/>
-      <c r="F115" s="1"/>
-      <c r="G115" s="1"/>
-      <c r="H115" s="2"/>
-      <c r="I115" s="11"/>
-      <c r="J115" s="23"/>
-      <c r="K115" s="1"/>
-    </row>
-    <row r="116" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="B116" s="9">
-        <v>46089</v>
-      </c>
-      <c r="C116" s="1"/>
-      <c r="D116" s="1"/>
-      <c r="E116" s="1"/>
-      <c r="F116" s="1"/>
-      <c r="G116" s="1"/>
-      <c r="H116" s="2"/>
-      <c r="I116" s="11"/>
-      <c r="J116" s="23"/>
-      <c r="K116" s="1"/>
-    </row>
-    <row r="117" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="B117" s="9">
-        <v>46090</v>
-      </c>
-      <c r="C117" s="1"/>
-      <c r="D117" s="1"/>
-      <c r="E117" s="1"/>
-      <c r="F117" s="1"/>
-      <c r="G117" s="1"/>
-      <c r="H117" s="2"/>
-      <c r="I117" s="11"/>
-      <c r="J117" s="23"/>
-      <c r="K117" s="1"/>
-    </row>
-    <row r="118" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="B118" s="9">
-        <v>46091</v>
-      </c>
-      <c r="C118" s="1"/>
-      <c r="D118" s="1"/>
-      <c r="E118" s="1"/>
-      <c r="F118" s="1"/>
-      <c r="G118" s="1"/>
-      <c r="H118" s="2"/>
-      <c r="I118" s="11"/>
-      <c r="J118" s="23"/>
-      <c r="K118" s="1"/>
-    </row>
-    <row r="119" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="B119" s="9">
-        <v>46092</v>
-      </c>
-      <c r="C119" s="1"/>
-      <c r="D119" s="1"/>
-      <c r="E119" s="1"/>
-      <c r="F119" s="1"/>
-      <c r="G119" s="1"/>
-      <c r="H119" s="2"/>
-      <c r="I119" s="11"/>
-      <c r="J119" s="23"/>
-      <c r="K119" s="1"/>
-    </row>
-    <row r="120" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="B120" s="9">
-        <v>46093</v>
-      </c>
-      <c r="C120" s="1"/>
-      <c r="D120" s="1"/>
-      <c r="E120" s="1"/>
-      <c r="F120" s="1"/>
-      <c r="G120" s="1"/>
-      <c r="H120" s="2"/>
-      <c r="I120" s="11"/>
-      <c r="J120" s="23"/>
-      <c r="K120" s="1"/>
-    </row>
-    <row r="121" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="B121" s="9">
-        <v>46094</v>
-      </c>
-      <c r="C121" s="1"/>
-      <c r="D121" s="1"/>
-      <c r="E121" s="1"/>
-      <c r="F121" s="1"/>
-      <c r="G121" s="1"/>
-      <c r="H121" s="2"/>
-      <c r="I121" s="11"/>
-      <c r="J121" s="23"/>
-      <c r="K121" s="1"/>
-    </row>
-    <row r="122" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="B122" s="9">
-        <v>46095</v>
-      </c>
-      <c r="C122" s="1"/>
-      <c r="D122" s="1"/>
-      <c r="E122" s="1"/>
-      <c r="F122" s="1"/>
-      <c r="G122" s="1"/>
-      <c r="H122" s="2"/>
-      <c r="I122" s="11"/>
-      <c r="J122" s="23"/>
-      <c r="K122" s="1"/>
-    </row>
-    <row r="123" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="B123" s="9">
-        <v>46096</v>
-      </c>
-      <c r="C123" s="1"/>
-      <c r="D123" s="1"/>
-      <c r="E123" s="1"/>
-      <c r="F123" s="1"/>
-      <c r="G123" s="1"/>
-      <c r="H123" s="2"/>
-      <c r="I123" s="11"/>
-      <c r="J123" s="23"/>
-      <c r="K123" s="1"/>
-    </row>
-    <row r="124" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="B124" s="9">
-        <v>46097</v>
-      </c>
-      <c r="C124" s="1"/>
-      <c r="D124" s="1"/>
-      <c r="E124" s="1"/>
-      <c r="F124" s="1"/>
-      <c r="G124" s="1"/>
-      <c r="H124" s="2"/>
-      <c r="I124" s="11"/>
-      <c r="J124" s="23"/>
-      <c r="K124" s="1"/>
-    </row>
-    <row r="125" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="B125" s="9">
-        <v>46098</v>
-      </c>
-      <c r="C125" s="1"/>
-      <c r="D125" s="1"/>
-      <c r="E125" s="1"/>
-      <c r="F125" s="1"/>
-      <c r="G125" s="1"/>
-      <c r="H125" s="2"/>
-      <c r="I125" s="11"/>
-      <c r="J125" s="23"/>
-      <c r="K125" s="1"/>
-    </row>
-    <row r="126" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="B126" s="9">
-        <v>46099</v>
-      </c>
-      <c r="C126" s="1"/>
-      <c r="D126" s="1"/>
-      <c r="E126" s="1"/>
-      <c r="F126" s="1"/>
-      <c r="G126" s="1"/>
-      <c r="H126" s="2"/>
-      <c r="I126" s="11"/>
-      <c r="J126" s="23"/>
-      <c r="K126" s="1"/>
-    </row>
-    <row r="127" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="B127" s="9">
-        <v>46100</v>
-      </c>
-      <c r="C127" s="1"/>
-      <c r="D127" s="1"/>
-      <c r="E127" s="1"/>
-      <c r="F127" s="1"/>
-      <c r="G127" s="1"/>
-      <c r="H127" s="2"/>
-      <c r="I127" s="11"/>
-      <c r="J127" s="23"/>
-      <c r="K127" s="1"/>
-    </row>
-    <row r="128" spans="2:11" ht="18" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B128" s="18">
-        <v>46101</v>
-      </c>
-      <c r="C128" s="19"/>
-      <c r="D128" s="19"/>
-      <c r="E128" s="19"/>
-      <c r="F128" s="19"/>
-      <c r="G128" s="19"/>
-      <c r="H128" s="20"/>
-      <c r="I128" s="21"/>
-      <c r="J128" s="24"/>
-      <c r="K128" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/data/ECN/ECN_STN_Master(SLH1).xlsx
+++ b/data/ECN/ECN_STN_Master(SLH1).xlsx
@@ -4763,7 +4763,7 @@
       <c r="J82" s="19" t="inlineStr"/>
       <c r="K82" s="20" t="inlineStr">
         <is>
-          <t>file://192.168.0.100/500%20%EC%83%9D%EC%82%B0/550%20%EA%B5%AD%EB%82%B4CS/ECT&amp;STN/SLH1-PP-260306-01(LD%20Manual%20Port).pdf</t>
+          <t>\\192.168.0.100\500 생산\550 국내CS\ECT&amp;STN\SLH1-PP-260306-01(LD Manual Port)</t>
         </is>
       </c>
     </row>

--- a/data/ECN/ECN_STN_Master(SLH1).xlsx
+++ b/data/ECN/ECN_STN_Master(SLH1).xlsx
@@ -4557,7 +4557,11 @@
       </c>
       <c r="I77" s="11" t="inlineStr"/>
       <c r="J77" s="19" t="inlineStr"/>
-      <c r="K77" s="20" t="inlineStr"/>
+      <c r="K77" s="20" t="inlineStr">
+        <is>
+          <t>\\192.168.0.100\500 생산\550 국내CS\ECT&amp;STN\ECN SLH1-PP-260219-02(CCTV BRK 신규추가)</t>
+        </is>
+      </c>
     </row>
     <row r="78" ht="156.6" customHeight="1" s="21">
       <c r="B78" s="9" t="n">
@@ -4599,7 +4603,11 @@
       </c>
       <c r="I78" s="11" t="inlineStr"/>
       <c r="J78" s="19" t="inlineStr"/>
-      <c r="K78" s="20" t="inlineStr"/>
+      <c r="K78" s="20" t="inlineStr">
+        <is>
+          <t>\\192.168.0.100\500 생산\550 국내CS\ECT&amp;STN\ECN SLH1-PP-260225-01(Tray Flow Preciser Insert Pitch Fitting 추가)</t>
+        </is>
+      </c>
     </row>
     <row r="79" ht="52.2" customHeight="1" s="21">
       <c r="B79" s="9" t="n">
@@ -4676,7 +4684,11 @@
       </c>
       <c r="I80" s="11" t="inlineStr"/>
       <c r="J80" s="19" t="inlineStr"/>
-      <c r="K80" s="20" t="inlineStr"/>
+      <c r="K80" s="20" t="inlineStr">
+        <is>
+          <t>\\192.168.0.100\500 생산\550 국내CS\ECT&amp;STN\SLH1-PP-260305-01(SOCAMM HAND 공압 변경 및 필터 추가)</t>
+        </is>
+      </c>
     </row>
     <row r="81" ht="104.4" customHeight="1" s="21">
       <c r="B81" s="9" t="n">
@@ -4717,7 +4729,11 @@
       </c>
       <c r="I81" s="11" t="inlineStr"/>
       <c r="J81" s="19" t="inlineStr"/>
-      <c r="K81" s="20" t="inlineStr"/>
+      <c r="K81" s="20" t="inlineStr">
+        <is>
+          <t>\\192.168.0.100\500 생산\550 국내CS\ECT&amp;STN\ECN SLH1-PP-260227-01(후면부 Regulator Sensor 위치 개선)</t>
+        </is>
+      </c>
     </row>
     <row r="82" ht="243.6" customHeight="1" s="21">
       <c r="B82" s="9" t="n">
@@ -4760,7 +4776,11 @@
         </is>
       </c>
       <c r="I82" s="11" t="inlineStr"/>
-      <c r="J82" s="19" t="inlineStr"/>
+      <c r="J82" s="19" t="inlineStr">
+        <is>
+          <t>횡전개 완료.</t>
+        </is>
+      </c>
       <c r="K82" s="20" t="inlineStr">
         <is>
           <t>\\192.168.0.100\500 생산\550 국내CS\ECT&amp;STN\SLH1-PP-260306-01(LD Manual Port)</t>

--- a/data/ECN/ECN_STN_Master(SLH1).xlsx
+++ b/data/ECN/ECN_STN_Master(SLH1).xlsx
@@ -4519,7 +4519,11 @@
       </c>
       <c r="I76" s="11" t="inlineStr"/>
       <c r="J76" s="19" t="inlineStr"/>
-      <c r="K76" s="20" t="inlineStr"/>
+      <c r="K76" s="20" t="inlineStr">
+        <is>
+          <t>\\192.168.0.100\500 생산\550 국내CS\ECT&amp;STN\ECN SLH1-PP-260219-02(CCTV BRK 신규추가)</t>
+        </is>
+      </c>
     </row>
     <row r="77" ht="34.8" customHeight="1" s="21">
       <c r="B77" s="9" t="n">
@@ -4559,7 +4563,7 @@
       <c r="J77" s="19" t="inlineStr"/>
       <c r="K77" s="20" t="inlineStr">
         <is>
-          <t>\\192.168.0.100\500 생산\550 국내CS\ECT&amp;STN\ECN SLH1-PP-260219-02(CCTV BRK 신규추가)</t>
+          <t>\\192.168.0.100\500 생산\550 국내CS\ECT&amp;STN\None</t>
         </is>
       </c>
     </row>

--- a/data/ECN/ECN_STN_Master(SLH1).xlsx
+++ b/data/ECN/ECN_STN_Master(SLH1).xlsx
@@ -4363,7 +4363,11 @@
       </c>
       <c r="I72" s="11" t="inlineStr"/>
       <c r="J72" s="19" t="inlineStr"/>
-      <c r="K72" s="20" t="inlineStr"/>
+      <c r="K72" s="20" t="inlineStr">
+        <is>
+          <t>\\192.168.0.100\500 생산\550 국내CS\ECT&amp;STN\SLH1-PP-260210-01(RDIMM Stacker Align BRK)</t>
+        </is>
+      </c>
     </row>
     <row r="73" ht="139.2" customHeight="1" s="21">
       <c r="B73" s="9" t="n">
@@ -4405,7 +4409,11 @@
       </c>
       <c r="I73" s="11" t="inlineStr"/>
       <c r="J73" s="19" t="inlineStr"/>
-      <c r="K73" s="20" t="inlineStr"/>
+      <c r="K73" s="20" t="inlineStr">
+        <is>
+          <t>\\192.168.0.100\500 생산\550 국내CS\ECT&amp;STN\SLH1-PP-260204-01(Transfer Tray Check Sensor 고정 BRK 길이 변경, 탭변경)</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="B74" s="9" t="n">
@@ -4481,7 +4489,11 @@
       </c>
       <c r="I75" s="11" t="inlineStr"/>
       <c r="J75" s="19" t="inlineStr"/>
-      <c r="K75" s="20" t="inlineStr"/>
+      <c r="K75" s="20" t="inlineStr">
+        <is>
+          <t>\\192.168.0.100\500 생산\550 국내CS\ECT&amp;STN\ECN SLH1-PP-260219-01(Conveyor Inverter 장착Pannel 모서리가드 추가)</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="B76" s="9" t="n">

--- a/data/ECN/ECN_STN_Master(SLH1).xlsx
+++ b/data/ECN/ECN_STN_Master(SLH1).xlsx
@@ -3961,7 +3961,11 @@
         </is>
       </c>
       <c r="J62" s="19" t="inlineStr"/>
-      <c r="K62" s="20" t="inlineStr"/>
+      <c r="K62" s="20" t="inlineStr">
+        <is>
+          <t>\\192.168.0.100\500 생산\550 국내CS\ECT&amp;STN\SLH1-PP-260123-01(낙수방지를 위한 TOP Cover 추가)</t>
+        </is>
+      </c>
     </row>
     <row r="63" ht="34.8" customHeight="1" s="21">
       <c r="B63" s="9" t="n">
@@ -4038,7 +4042,11 @@
       </c>
       <c r="I64" s="11" t="inlineStr"/>
       <c r="J64" s="19" t="inlineStr"/>
-      <c r="K64" s="20" t="inlineStr"/>
+      <c r="K64" s="20" t="inlineStr">
+        <is>
+          <t>\\192.168.0.100\500 생산\550 국내CS\ECT&amp;STN\SLH1-PP-260127-01(Hand Picker EDS 부적격으로 마크리스 특수코팅추가)</t>
+        </is>
+      </c>
     </row>
     <row r="65" ht="69.59999999999999" customHeight="1" s="21">
       <c r="B65" s="9" t="n">
@@ -4079,7 +4087,11 @@
       </c>
       <c r="I65" s="11" t="inlineStr"/>
       <c r="J65" s="19" t="inlineStr"/>
-      <c r="K65" s="20" t="inlineStr"/>
+      <c r="K65" s="20" t="inlineStr">
+        <is>
+          <t>\\192.168.0.100\500 생산\550 국내CS\ECT&amp;STN\SLH1-PP-260126-01(Rear Cover Bolt와 덕트 간섭으로 상대물에 Tap추가)</t>
+        </is>
+      </c>
     </row>
     <row r="66" ht="52.2" customHeight="1" s="21">
       <c r="B66" s="9" t="n">
@@ -4119,7 +4131,11 @@
       </c>
       <c r="I66" s="11" t="inlineStr"/>
       <c r="J66" s="19" t="inlineStr"/>
-      <c r="K66" s="20" t="inlineStr"/>
+      <c r="K66" s="20" t="inlineStr">
+        <is>
+          <t>\\192.168.0.100\500 생산\550 국내CS\ECT&amp;STN\SLH1-PP-260128-01(Transfer Support Shaft 크기 축소)</t>
+        </is>
+      </c>
     </row>
     <row r="67" ht="34.8" customHeight="1" s="21">
       <c r="B67" s="9" t="n">
@@ -4158,7 +4174,11 @@
       </c>
       <c r="I67" s="11" t="inlineStr"/>
       <c r="J67" s="19" t="inlineStr"/>
-      <c r="K67" s="20" t="inlineStr"/>
+      <c r="K67" s="20" t="inlineStr">
+        <is>
+          <t>\\192.168.0.100\500 생산\550 국내CS\ECT&amp;STN\SLH1-PP-260127-02(Flow Rail 타가이드 두께변경）</t>
+        </is>
+      </c>
     </row>
     <row r="68" ht="69.59999999999999" customHeight="1" s="21">
       <c r="B68" s="9" t="n">
@@ -4279,7 +4299,11 @@
       </c>
       <c r="I70" s="11" t="inlineStr"/>
       <c r="J70" s="19" t="inlineStr"/>
-      <c r="K70" s="20" t="inlineStr"/>
+      <c r="K70" s="20" t="inlineStr">
+        <is>
+          <t>\\192.168.0.100\500 생산\550 국내CS\ECT&amp;STN\ECN SLH1-TP-260122-01（Socamm BCR Block 추가）</t>
+        </is>
+      </c>
     </row>
     <row r="71" ht="87" customHeight="1" s="21">
       <c r="B71" s="9" t="n">
@@ -4319,7 +4343,11 @@
       </c>
       <c r="I71" s="11" t="inlineStr"/>
       <c r="J71" s="19" t="inlineStr"/>
-      <c r="K71" s="20" t="inlineStr"/>
+      <c r="K71" s="20" t="inlineStr">
+        <is>
+          <t>\\192.168.0.100\500 생산\550 국내CS\ECT&amp;STN\SLH1-PP-260205-01(Reject Stacker Align BRK 장공크기 조정 및 불필요 장공 삭제)</t>
+        </is>
+      </c>
     </row>
     <row r="72" ht="139.2" customHeight="1" s="21">
       <c r="B72" s="9" t="n">

--- a/data/ECN/ECN_STN_Master(SLH1).xlsx
+++ b/data/ECN/ECN_STN_Master(SLH1).xlsx
@@ -3963,7 +3963,7 @@
       <c r="J62" s="19" t="inlineStr"/>
       <c r="K62" s="20" t="inlineStr">
         <is>
-          <t>\\192.168.0.100\500 생산\550 국내CS\ECT&amp;STN\SLH1-PP-260123-01(낙수방지를 위한 TOP Cover 추가)</t>
+          <t>\\192.168.0.100\500 생산\550 국내CS\ECT&amp;STN\None</t>
         </is>
       </c>
     </row>
@@ -4004,7 +4004,11 @@
       </c>
       <c r="I63" s="11" t="inlineStr"/>
       <c r="J63" s="19" t="inlineStr"/>
-      <c r="K63" s="20" t="inlineStr"/>
+      <c r="K63" s="20" t="inlineStr">
+        <is>
+          <t>\\192.168.0.100\500 생산\550 국내CS\ECT&amp;STN\SLH1-PP-260123-01(낙수방지를 위한 TOP Cover 추가)</t>
+        </is>
+      </c>
     </row>
     <row r="64" ht="34.8" customHeight="1" s="21">
       <c r="B64" s="9" t="n">

--- a/data/ECN/ECN_STN_Master(SLH1).xlsx
+++ b/data/ECN/ECN_STN_Master(SLH1).xlsx
@@ -3648,7 +3648,11 @@
       </c>
       <c r="I54" s="11" t="inlineStr"/>
       <c r="J54" s="19" t="inlineStr"/>
-      <c r="K54" s="20" t="inlineStr"/>
+      <c r="K54" s="20" t="inlineStr">
+        <is>
+          <t>\\192.168.0.100\500 생산\550 국내CS\ECT&amp;STN\SLH1-PP-260112-01(5건)</t>
+        </is>
+      </c>
     </row>
     <row r="55" ht="52.2" customHeight="1" s="21">
       <c r="B55" s="9" t="n">
@@ -3688,7 +3692,11 @@
       </c>
       <c r="I55" s="11" t="inlineStr"/>
       <c r="J55" s="19" t="inlineStr"/>
-      <c r="K55" s="20" t="inlineStr"/>
+      <c r="K55" s="20" t="inlineStr">
+        <is>
+          <t>\\192.168.0.100\500 생산\550 국내CS\ECT&amp;STN\SLH1-PP-260115-01(Tary Flow 상단 LED 설치 Tap 누락으로 추가)</t>
+        </is>
+      </c>
     </row>
     <row r="56" ht="34.8" customHeight="1" s="21">
       <c r="B56" s="9" t="n">
@@ -3765,7 +3773,11 @@
       </c>
       <c r="I57" s="11" t="inlineStr"/>
       <c r="J57" s="19" t="inlineStr"/>
-      <c r="K57" s="20" t="inlineStr"/>
+      <c r="K57" s="20" t="inlineStr">
+        <is>
+          <t>\\192.168.0.100\500 생산\550 국내CS\ECT&amp;STN\SLH1-PP-260119-01(SetPlate Indigator Cover 탭장공,홀 탭 변경,Size 변경)</t>
+        </is>
+      </c>
     </row>
     <row r="58" ht="34.8" customHeight="1" s="21">
       <c r="B58" s="9" t="n">
@@ -3843,7 +3855,11 @@
       </c>
       <c r="I59" s="11" t="inlineStr"/>
       <c r="J59" s="19" t="inlineStr"/>
-      <c r="K59" s="20" t="inlineStr"/>
+      <c r="K59" s="20" t="inlineStr">
+        <is>
+          <t>\\192.168.0.100\500 생산\550 국내CS\ECT&amp;STN\SLH1-PP-260121-01(Align Guide 1 하단 Block 추가)</t>
+        </is>
+      </c>
     </row>
     <row r="60" ht="34.8" customHeight="1" s="21">
       <c r="B60" s="9" t="n">

--- a/data/ECN/ECN_STN_Master(SLH1).xlsx
+++ b/data/ECN/ECN_STN_Master(SLH1).xlsx
@@ -3650,7 +3650,7 @@
       <c r="J54" s="19" t="inlineStr"/>
       <c r="K54" s="20" t="inlineStr">
         <is>
-          <t>\\192.168.0.100\500 생산\550 국내CS\ECT&amp;STN\SLH1-PP-260112-01(5건)</t>
+          <t>\\192.168.0.100\500 생산\550 국내CS\ECN&amp;STN\SLH1-PP-260112-01(5건).pdf</t>
         </is>
       </c>
     </row>
@@ -3694,7 +3694,7 @@
       <c r="J55" s="19" t="inlineStr"/>
       <c r="K55" s="20" t="inlineStr">
         <is>
-          <t>\\192.168.0.100\500 생산\550 국내CS\ECT&amp;STN\SLH1-PP-260115-01(Tary Flow 상단 LED 설치 Tap 누락으로 추가)</t>
+          <t>\\192.168.0.100\500 생산\550 국내CS\ECN&amp;STN\SLH1-PP-260115-01(Tary Flow 상단 LED 설치 Tap 누락으로 추가).pdf</t>
         </is>
       </c>
     </row>
@@ -3775,7 +3775,7 @@
       <c r="J57" s="19" t="inlineStr"/>
       <c r="K57" s="20" t="inlineStr">
         <is>
-          <t>\\192.168.0.100\500 생산\550 국내CS\ECT&amp;STN\SLH1-PP-260119-01(SetPlate Indigator Cover 탭장공,홀 탭 변경,Size 변경)</t>
+          <t>\\192.168.0.100\500 생산\550 국내CS\ECN&amp;STN\SLH1-PP-260119-01(SetPlate Indigator Cover 탭장공,홀 탭 변경,Size 변경).pdf</t>
         </is>
       </c>
     </row>
@@ -3857,7 +3857,7 @@
       <c r="J59" s="19" t="inlineStr"/>
       <c r="K59" s="20" t="inlineStr">
         <is>
-          <t>\\192.168.0.100\500 생산\550 국내CS\ECT&amp;STN\SLH1-PP-260121-01(Align Guide 1 하단 Block 추가)</t>
+          <t>\\192.168.0.100\500 생산\550 국내CS\ECN&amp;STN\SLH1-PP-260121-01(Align Guide 1 하단 Block 추가).pdf</t>
         </is>
       </c>
     </row>
@@ -3979,7 +3979,7 @@
       <c r="J62" s="19" t="inlineStr"/>
       <c r="K62" s="20" t="inlineStr">
         <is>
-          <t>\\192.168.0.100\500 생산\550 국내CS\ECT&amp;STN\None</t>
+          <t>\\192.168.0.100\500 생산\550 국내CS\ECN&amp;STN\None.pdf</t>
         </is>
       </c>
     </row>
@@ -4022,7 +4022,7 @@
       <c r="J63" s="19" t="inlineStr"/>
       <c r="K63" s="20" t="inlineStr">
         <is>
-          <t>\\192.168.0.100\500 생산\550 국내CS\ECT&amp;STN\SLH1-PP-260123-01(낙수방지를 위한 TOP Cover 추가)</t>
+          <t>\\192.168.0.100\500 생산\550 국내CS\ECN&amp;STN\SLH1-PP-260123-01(낙수방지를 위한 TOP Cover 추가).pdf</t>
         </is>
       </c>
     </row>
@@ -4064,7 +4064,7 @@
       <c r="J64" s="19" t="inlineStr"/>
       <c r="K64" s="20" t="inlineStr">
         <is>
-          <t>\\192.168.0.100\500 생산\550 국내CS\ECT&amp;STN\SLH1-PP-260127-01(Hand Picker EDS 부적격으로 마크리스 특수코팅추가)</t>
+          <t>\\192.168.0.100\500 생산\550 국내CS\ECN&amp;STN\SLH1-PP-260127-01(Hand Picker EDS 부적격으로 마크리스 특수코팅추가).pdf</t>
         </is>
       </c>
     </row>
@@ -4109,7 +4109,7 @@
       <c r="J65" s="19" t="inlineStr"/>
       <c r="K65" s="20" t="inlineStr">
         <is>
-          <t>\\192.168.0.100\500 생산\550 국내CS\ECT&amp;STN\SLH1-PP-260126-01(Rear Cover Bolt와 덕트 간섭으로 상대물에 Tap추가)</t>
+          <t>\\192.168.0.100\500 생산\550 국내CS\ECN&amp;STN\SLH1-PP-260126-01(Rear Cover Bolt와 덕트 간섭으로 상대물에 Tap추가).pdf</t>
         </is>
       </c>
     </row>
@@ -4153,7 +4153,7 @@
       <c r="J66" s="19" t="inlineStr"/>
       <c r="K66" s="20" t="inlineStr">
         <is>
-          <t>\\192.168.0.100\500 생산\550 국내CS\ECT&amp;STN\SLH1-PP-260128-01(Transfer Support Shaft 크기 축소)</t>
+          <t>\\192.168.0.100\500 생산\550 국내CS\ECN&amp;STN\SLH1-PP-260128-01(Transfer Support Shaft 크기 축소).pdf</t>
         </is>
       </c>
     </row>
@@ -4196,7 +4196,7 @@
       <c r="J67" s="19" t="inlineStr"/>
       <c r="K67" s="20" t="inlineStr">
         <is>
-          <t>\\192.168.0.100\500 생산\550 국내CS\ECT&amp;STN\SLH1-PP-260127-02(Flow Rail 타가이드 두께변경）</t>
+          <t>\\192.168.0.100\500 생산\550 국내CS\ECN&amp;STN\SLH1-PP-260127-02(Flow Rail 타가이드 두께변경）.pdf</t>
         </is>
       </c>
     </row>
@@ -4321,7 +4321,7 @@
       <c r="J70" s="19" t="inlineStr"/>
       <c r="K70" s="20" t="inlineStr">
         <is>
-          <t>\\192.168.0.100\500 생산\550 국내CS\ECT&amp;STN\ECN SLH1-TP-260122-01（Socamm BCR Block 추가）</t>
+          <t>\\192.168.0.100\500 생산\550 국내CS\ECN&amp;STN\ECN SLH1-TP-260122-01（Socamm BCR Block 추가）.pdf</t>
         </is>
       </c>
     </row>
@@ -4365,7 +4365,7 @@
       <c r="J71" s="19" t="inlineStr"/>
       <c r="K71" s="20" t="inlineStr">
         <is>
-          <t>\\192.168.0.100\500 생산\550 국내CS\ECT&amp;STN\SLH1-PP-260205-01(Reject Stacker Align BRK 장공크기 조정 및 불필요 장공 삭제)</t>
+          <t>\\192.168.0.100\500 생산\550 국내CS\ECN&amp;STN\SLH1-PP-260205-01(Reject Stacker Align BRK 장공크기 조정 및 불필요 장공 삭제).pdf</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4413,7 @@
       <c r="J72" s="19" t="inlineStr"/>
       <c r="K72" s="20" t="inlineStr">
         <is>
-          <t>\\192.168.0.100\500 생산\550 국내CS\ECT&amp;STN\SLH1-PP-260210-01(RDIMM Stacker Align BRK)</t>
+          <t>\\192.168.0.100\500 생산\550 국내CS\ECN&amp;STN\SLH1-PP-260210-01(RDIMM Stacker Align BRK).pdf</t>
         </is>
       </c>
     </row>
@@ -4459,7 +4459,7 @@
       <c r="J73" s="19" t="inlineStr"/>
       <c r="K73" s="20" t="inlineStr">
         <is>
-          <t>\\192.168.0.100\500 생산\550 국내CS\ECT&amp;STN\SLH1-PP-260204-01(Transfer Tray Check Sensor 고정 BRK 길이 변경, 탭변경)</t>
+          <t>\\192.168.0.100\500 생산\550 국내CS\ECN&amp;STN\SLH1-PP-260204-01(Transfer Tray Check Sensor 고정 BRK 길이 변경, 탭변경).pdf</t>
         </is>
       </c>
     </row>
@@ -4539,7 +4539,7 @@
       <c r="J75" s="19" t="inlineStr"/>
       <c r="K75" s="20" t="inlineStr">
         <is>
-          <t>\\192.168.0.100\500 생산\550 국내CS\ECT&amp;STN\ECN SLH1-PP-260219-01(Conveyor Inverter 장착Pannel 모서리가드 추가)</t>
+          <t>\\192.168.0.100\500 생산\550 국내CS\ECN&amp;STN\ECN SLH1-PP-260219-01(Conveyor Inverter 장착Pannel 모서리가드 추가).pdf</t>
         </is>
       </c>
     </row>
@@ -4581,7 +4581,7 @@
       <c r="J76" s="19" t="inlineStr"/>
       <c r="K76" s="20" t="inlineStr">
         <is>
-          <t>\\192.168.0.100\500 생산\550 국내CS\ECT&amp;STN\ECN SLH1-PP-260219-02(CCTV BRK 신규추가)</t>
+          <t>\\192.168.0.100\500 생산\550 국내CS\ECN&amp;STN\ECN SLH1-PP-260219-02(CCTV BRK 신규추가).pdf</t>
         </is>
       </c>
     </row>
@@ -4623,7 +4623,7 @@
       <c r="J77" s="19" t="inlineStr"/>
       <c r="K77" s="20" t="inlineStr">
         <is>
-          <t>\\192.168.0.100\500 생산\550 국내CS\ECT&amp;STN\None</t>
+          <t>\\192.168.0.100\500 생산\550 국내CS\ECN&amp;STN\None.pdf</t>
         </is>
       </c>
     </row>
@@ -4669,7 +4669,7 @@
       <c r="J78" s="19" t="inlineStr"/>
       <c r="K78" s="20" t="inlineStr">
         <is>
-          <t>\\192.168.0.100\500 생산\550 국내CS\ECT&amp;STN\ECN SLH1-PP-260225-01(Tray Flow Preciser Insert Pitch Fitting 추가)</t>
+          <t>\\192.168.0.100\500 생산\550 국내CS\ECN&amp;STN\ECN SLH1-PP-260225-01(Tray Flow Preciser Insert Pitch Fitting 추가).pdf</t>
         </is>
       </c>
     </row>
@@ -4750,7 +4750,7 @@
       <c r="J80" s="19" t="inlineStr"/>
       <c r="K80" s="20" t="inlineStr">
         <is>
-          <t>\\192.168.0.100\500 생산\550 국내CS\ECT&amp;STN\SLH1-PP-260305-01(SOCAMM HAND 공압 변경 및 필터 추가)</t>
+          <t>\\192.168.0.100\500 생산\550 국내CS\ECN&amp;STN\SLH1-PP-260305-01(SOCAMM HAND 공압 변경 및 필터 추가).pdf</t>
         </is>
       </c>
     </row>
@@ -4795,7 +4795,7 @@
       <c r="J81" s="19" t="inlineStr"/>
       <c r="K81" s="20" t="inlineStr">
         <is>
-          <t>\\192.168.0.100\500 생산\550 국내CS\ECT&amp;STN\ECN SLH1-PP-260227-01(후면부 Regulator Sensor 위치 개선)</t>
+          <t>\\192.168.0.100\500 생산\550 국내CS\ECN&amp;STN\ECN SLH1-PP-260227-01(후면부 Regulator Sensor 위치 개선).pdf</t>
         </is>
       </c>
     </row>
@@ -4847,7 +4847,7 @@
       </c>
       <c r="K82" s="20" t="inlineStr">
         <is>
-          <t>\\192.168.0.100\500 생산\550 국내CS\ECT&amp;STN\SLH1-PP-260306-01(LD Manual Port)</t>
+          <t>\\192.168.0.100\500 생산\550 국내CS\ECN&amp;STN\SLH1-PP-260306-01(LD Manual Port).pdf</t>
         </is>
       </c>
     </row>

--- a/data/ECN/ECN_STN_Master(SLH1).xlsx
+++ b/data/ECN/ECN_STN_Master(SLH1).xlsx
@@ -1585,7 +1585,9 @@
           <t xml:space="preserve">11-17일 입고 요청 </t>
         </is>
       </c>
-      <c r="J4" s="19" t="inlineStr"/>
+      <c r="J4" s="19" t="n">
+        <v/>
+      </c>
       <c r="K4" s="20" t="inlineStr"/>
     </row>
     <row r="5" ht="276" customHeight="1" s="21">
@@ -1640,7 +1642,9 @@
           <t>11~26 입고 요청</t>
         </is>
       </c>
-      <c r="J5" s="19" t="inlineStr"/>
+      <c r="J5" s="19" t="n">
+        <v/>
+      </c>
       <c r="K5" s="20" t="inlineStr"/>
     </row>
     <row r="6" ht="87" customHeight="1" s="21">
@@ -1683,7 +1687,9 @@
           <t>11~28 입고 요청</t>
         </is>
       </c>
-      <c r="J6" s="19" t="inlineStr"/>
+      <c r="J6" s="19" t="n">
+        <v/>
+      </c>
       <c r="K6" s="20" t="inlineStr"/>
     </row>
     <row r="7">
@@ -1721,7 +1727,9 @@
           <t>11~28일 입고 요청</t>
         </is>
       </c>
-      <c r="J7" s="19" t="inlineStr"/>
+      <c r="J7" s="19" t="n">
+        <v/>
+      </c>
       <c r="K7" s="20" t="inlineStr"/>
     </row>
     <row r="8" ht="34.8" customHeight="1" s="21">
@@ -1754,8 +1762,12 @@
         </is>
       </c>
       <c r="H8" s="2" t="n"/>
-      <c r="I8" s="11" t="inlineStr"/>
-      <c r="J8" s="19" t="inlineStr"/>
+      <c r="I8" s="11" t="n">
+        <v/>
+      </c>
+      <c r="J8" s="19" t="n">
+        <v/>
+      </c>
       <c r="K8" s="20" t="inlineStr"/>
     </row>
     <row r="9" ht="69.59999999999999" customHeight="1" s="21">
@@ -1796,8 +1808,12 @@
 -현재 SLH1 PC는 USB 3.0 PORT 로 구성되어있음</t>
         </is>
       </c>
-      <c r="I9" s="11" t="inlineStr"/>
-      <c r="J9" s="19" t="inlineStr"/>
+      <c r="I9" s="11" t="n">
+        <v/>
+      </c>
+      <c r="J9" s="19" t="n">
+        <v/>
+      </c>
       <c r="K9" s="20" t="inlineStr"/>
     </row>
     <row r="10" ht="69.59999999999999" customHeight="1" s="21">
@@ -1840,7 +1856,9 @@
           <t>11~28일 입고 요청</t>
         </is>
       </c>
-      <c r="J10" s="19" t="inlineStr"/>
+      <c r="J10" s="19" t="n">
+        <v/>
+      </c>
       <c r="K10" s="20" t="inlineStr"/>
     </row>
     <row r="11" ht="34.8" customFormat="1" customHeight="1" s="16">
@@ -1878,8 +1896,12 @@
           <t>-RD Tray Bending 개선, Rail 갈림현상 개선 -LPCAMM Tray Rail 갈림현상 개선</t>
         </is>
       </c>
-      <c r="I11" s="11" t="inlineStr"/>
-      <c r="J11" s="19" t="inlineStr"/>
+      <c r="I11" s="11" t="n">
+        <v/>
+      </c>
+      <c r="J11" s="19" t="n">
+        <v/>
+      </c>
       <c r="K11" s="20" t="inlineStr"/>
     </row>
     <row r="12" ht="34.8" customFormat="1" customHeight="1" s="16">
@@ -1917,8 +1939,12 @@
           <t>SLH1 RD 최종 Insert(Latch 제거) 및 T-tray Bom Update</t>
         </is>
       </c>
-      <c r="I12" s="11" t="inlineStr"/>
-      <c r="J12" s="19" t="inlineStr"/>
+      <c r="I12" s="11" t="n">
+        <v/>
+      </c>
+      <c r="J12" s="19" t="n">
+        <v/>
+      </c>
       <c r="K12" s="20" t="inlineStr"/>
     </row>
     <row r="13">
@@ -1960,7 +1986,9 @@
           <t>12~01일 입고 요청</t>
         </is>
       </c>
-      <c r="J13" s="19" t="inlineStr"/>
+      <c r="J13" s="19" t="n">
+        <v/>
+      </c>
       <c r="K13" s="20" t="inlineStr"/>
     </row>
     <row r="14" ht="121.8" customHeight="1" s="21">
@@ -2006,7 +2034,9 @@
           <t>12~2일 입고 요청</t>
         </is>
       </c>
-      <c r="J14" s="19" t="inlineStr"/>
+      <c r="J14" s="19" t="n">
+        <v/>
+      </c>
       <c r="K14" s="20" t="inlineStr"/>
     </row>
     <row r="15">
@@ -2043,8 +2073,12 @@
           <t>SLH1 RD 최종 INSERT 수량 정정(1ea&gt;16ea)</t>
         </is>
       </c>
-      <c r="I15" s="11" t="inlineStr"/>
-      <c r="J15" s="19" t="inlineStr"/>
+      <c r="I15" s="11" t="n">
+        <v/>
+      </c>
+      <c r="J15" s="19" t="n">
+        <v/>
+      </c>
       <c r="K15" s="20" t="inlineStr"/>
     </row>
     <row r="16" ht="40.95" customHeight="1" s="21">
@@ -2081,8 +2115,12 @@
           <t>플러팅 기능 불가로 인한 가공 추가(선진행 요청)</t>
         </is>
       </c>
-      <c r="I16" s="11" t="inlineStr"/>
-      <c r="J16" s="19" t="inlineStr"/>
+      <c r="I16" s="11" t="n">
+        <v/>
+      </c>
+      <c r="J16" s="19" t="n">
+        <v/>
+      </c>
       <c r="K16" s="20" t="inlineStr"/>
     </row>
     <row r="17" ht="156" customHeight="1" s="21">
@@ -2130,7 +2168,9 @@
           <t>12~5일 입고 요청</t>
         </is>
       </c>
-      <c r="J17" s="19" t="inlineStr"/>
+      <c r="J17" s="19" t="n">
+        <v/>
+      </c>
       <c r="K17" s="20" t="inlineStr"/>
     </row>
     <row r="18" ht="135" customHeight="1" s="21">
@@ -2176,7 +2216,9 @@
           <t>12~4일 입고 요청</t>
         </is>
       </c>
-      <c r="J18" s="19" t="inlineStr"/>
+      <c r="J18" s="19" t="n">
+        <v/>
+      </c>
       <c r="K18" s="20" t="inlineStr"/>
     </row>
     <row r="19" ht="180" customHeight="1" s="21">
@@ -2218,8 +2260,12 @@
  - LM과 조립 불가로 조립 기준 변경</t>
         </is>
       </c>
-      <c r="I19" s="11" t="inlineStr"/>
-      <c r="J19" s="19" t="inlineStr"/>
+      <c r="I19" s="11" t="n">
+        <v/>
+      </c>
+      <c r="J19" s="19" t="n">
+        <v/>
+      </c>
       <c r="K19" s="20" t="inlineStr"/>
     </row>
     <row r="20" ht="121.8" customHeight="1" s="21">
@@ -2267,7 +2313,9 @@
           <t>12~9일 입고요청</t>
         </is>
       </c>
-      <c r="J20" s="19" t="inlineStr"/>
+      <c r="J20" s="19" t="n">
+        <v/>
+      </c>
       <c r="K20" s="20" t="inlineStr"/>
     </row>
     <row r="21" ht="87" customHeight="1" s="21">
@@ -2313,7 +2361,9 @@
           <t>12~12일 입고요청</t>
         </is>
       </c>
-      <c r="J21" s="19" t="inlineStr"/>
+      <c r="J21" s="19" t="n">
+        <v/>
+      </c>
       <c r="K21" s="20" t="inlineStr"/>
     </row>
     <row r="22" ht="128.4" customHeight="1" s="21">
@@ -2355,8 +2405,12 @@
 -도면 업데이트 및 부적합 사항 수정</t>
         </is>
       </c>
-      <c r="I22" s="11" t="inlineStr"/>
-      <c r="J22" s="19" t="inlineStr"/>
+      <c r="I22" s="11" t="n">
+        <v/>
+      </c>
+      <c r="J22" s="19" t="n">
+        <v/>
+      </c>
       <c r="K22" s="20" t="inlineStr"/>
     </row>
     <row r="23" ht="87" customHeight="1" s="21">
@@ -2397,8 +2451,12 @@
 -신규 STOPPER 발주</t>
         </is>
       </c>
-      <c r="I23" s="11" t="inlineStr"/>
-      <c r="J23" s="19" t="inlineStr"/>
+      <c r="I23" s="11" t="n">
+        <v/>
+      </c>
+      <c r="J23" s="19" t="n">
+        <v/>
+      </c>
       <c r="K23" s="20" t="inlineStr"/>
     </row>
     <row r="24" ht="52.2" customHeight="1" s="21">
@@ -2437,8 +2495,12 @@
 -Cover의 풀림 방지를 위한 너트 추가</t>
         </is>
       </c>
-      <c r="I24" s="11" t="inlineStr"/>
-      <c r="J24" s="19" t="inlineStr"/>
+      <c r="I24" s="11" t="n">
+        <v/>
+      </c>
+      <c r="J24" s="19" t="n">
+        <v/>
+      </c>
       <c r="K24" s="20" t="inlineStr"/>
     </row>
     <row r="25" ht="69.59999999999999" customHeight="1" s="21">
@@ -2478,8 +2540,12 @@
 -크기 및 성능 동일 하며 CE 및 UL 인증 확인 완료.</t>
         </is>
       </c>
-      <c r="I25" s="11" t="inlineStr"/>
-      <c r="J25" s="19" t="inlineStr"/>
+      <c r="I25" s="11" t="n">
+        <v/>
+      </c>
+      <c r="J25" s="19" t="n">
+        <v/>
+      </c>
       <c r="K25" s="20" t="inlineStr"/>
     </row>
     <row r="26" ht="104.4" customHeight="1" s="21">
@@ -2519,8 +2585,12 @@
 -1호기 때 조립기준과 달라져 배선 방향 변경으로 길이 변경하여 포설 필요</t>
         </is>
       </c>
-      <c r="I26" s="11" t="inlineStr"/>
-      <c r="J26" s="19" t="inlineStr"/>
+      <c r="I26" s="11" t="n">
+        <v/>
+      </c>
+      <c r="J26" s="19" t="n">
+        <v/>
+      </c>
       <c r="K26" s="20" t="inlineStr"/>
     </row>
     <row r="27" ht="190.8" customHeight="1" s="21">
@@ -2566,8 +2636,12 @@
  - 간섭 미사용 구매품 폐기</t>
         </is>
       </c>
-      <c r="I27" s="11" t="inlineStr"/>
-      <c r="J27" s="19" t="inlineStr"/>
+      <c r="I27" s="11" t="n">
+        <v/>
+      </c>
+      <c r="J27" s="19" t="n">
+        <v/>
+      </c>
       <c r="K27" s="20" t="inlineStr"/>
     </row>
     <row r="28" ht="52.2" customHeight="1" s="21">
@@ -2605,8 +2679,12 @@
 -제조팀 요청 공압 선 정리를 위한 홀 추가</t>
         </is>
       </c>
-      <c r="I28" s="11" t="inlineStr"/>
-      <c r="J28" s="19" t="inlineStr"/>
+      <c r="I28" s="11" t="n">
+        <v/>
+      </c>
+      <c r="J28" s="19" t="n">
+        <v/>
+      </c>
       <c r="K28" s="20" t="inlineStr"/>
     </row>
     <row r="29">
@@ -2643,8 +2721,12 @@
           <t>잦은 파손으로 인한 재질 및 후처리 변경</t>
         </is>
       </c>
-      <c r="I29" s="11" t="inlineStr"/>
-      <c r="J29" s="19" t="inlineStr"/>
+      <c r="I29" s="11" t="n">
+        <v/>
+      </c>
+      <c r="J29" s="19" t="n">
+        <v/>
+      </c>
       <c r="K29" s="20" t="inlineStr"/>
     </row>
     <row r="30">
@@ -2681,8 +2763,12 @@
           <t>고객사 요청 가공품 재질 및 후처리 변경</t>
         </is>
       </c>
-      <c r="I30" s="11" t="inlineStr"/>
-      <c r="J30" s="19" t="inlineStr"/>
+      <c r="I30" s="11" t="n">
+        <v/>
+      </c>
+      <c r="J30" s="19" t="n">
+        <v/>
+      </c>
       <c r="K30" s="20" t="inlineStr"/>
     </row>
     <row r="31" ht="87" customHeight="1" s="21">
@@ -2723,8 +2809,12 @@
 -치수 누락으로 인한 도면 UPDATE (현품수정)</t>
         </is>
       </c>
-      <c r="I31" s="11" t="inlineStr"/>
-      <c r="J31" s="19" t="inlineStr"/>
+      <c r="I31" s="11" t="n">
+        <v/>
+      </c>
+      <c r="J31" s="19" t="n">
+        <v/>
+      </c>
       <c r="K31" s="20" t="inlineStr"/>
     </row>
     <row r="32">
@@ -2761,8 +2851,12 @@
           <t>FITTING 연결부 크기 미일치로 인해 FITTING변경</t>
         </is>
       </c>
-      <c r="I32" s="11" t="inlineStr"/>
-      <c r="J32" s="19" t="inlineStr"/>
+      <c r="I32" s="11" t="n">
+        <v/>
+      </c>
+      <c r="J32" s="19" t="n">
+        <v/>
+      </c>
       <c r="K32" s="20" t="inlineStr"/>
     </row>
     <row r="33" ht="69.59999999999999" customHeight="1" s="21">
@@ -2802,8 +2896,12 @@
 -모니터 회전의 어려움으로 인한 샤프트 길이 변경</t>
         </is>
       </c>
-      <c r="I33" s="11" t="inlineStr"/>
-      <c r="J33" s="19" t="inlineStr"/>
+      <c r="I33" s="11" t="n">
+        <v/>
+      </c>
+      <c r="J33" s="19" t="n">
+        <v/>
+      </c>
       <c r="K33" s="20" t="inlineStr"/>
     </row>
     <row r="34" ht="34.8" customHeight="1" s="21">
@@ -2841,8 +2939,12 @@
 -전장판 떨림 방지 개선</t>
         </is>
       </c>
-      <c r="I34" s="11" t="inlineStr"/>
-      <c r="J34" s="19" t="inlineStr"/>
+      <c r="I34" s="11" t="n">
+        <v/>
+      </c>
+      <c r="J34" s="19" t="n">
+        <v/>
+      </c>
       <c r="K34" s="20" t="inlineStr"/>
     </row>
     <row r="35" ht="226.2" customHeight="1" s="21">
@@ -2886,8 +2988,12 @@
 -D컷 가공 추가</t>
         </is>
       </c>
-      <c r="I35" s="11" t="inlineStr"/>
-      <c r="J35" s="19" t="inlineStr"/>
+      <c r="I35" s="11" t="n">
+        <v/>
+      </c>
+      <c r="J35" s="19" t="n">
+        <v/>
+      </c>
       <c r="K35" s="20" t="inlineStr"/>
     </row>
     <row r="36" ht="87" customHeight="1" s="21">
@@ -2928,8 +3034,12 @@
 -제조팀 요청 솔블록 추가</t>
         </is>
       </c>
-      <c r="I36" s="11" t="inlineStr"/>
-      <c r="J36" s="19" t="inlineStr"/>
+      <c r="I36" s="11" t="n">
+        <v/>
+      </c>
+      <c r="J36" s="19" t="n">
+        <v/>
+      </c>
       <c r="K36" s="20" t="inlineStr"/>
     </row>
     <row r="37" ht="69.59999999999999" customHeight="1" s="21">
@@ -2969,8 +3079,12 @@
 -탭 위치 불량으로 인한 탭 추가</t>
         </is>
       </c>
-      <c r="I37" s="11" t="inlineStr"/>
-      <c r="J37" s="19" t="inlineStr"/>
+      <c r="I37" s="11" t="n">
+        <v/>
+      </c>
+      <c r="J37" s="19" t="n">
+        <v/>
+      </c>
       <c r="K37" s="20" t="inlineStr"/>
     </row>
     <row r="38" ht="69.59999999999999" customHeight="1" s="21">
@@ -3009,8 +3123,12 @@
 -STACKER STOPPER 흐트러짐 개선 건(1호기 테스트 완료)</t>
         </is>
       </c>
-      <c r="I38" s="11" t="inlineStr"/>
-      <c r="J38" s="19" t="inlineStr"/>
+      <c r="I38" s="11" t="n">
+        <v/>
+      </c>
+      <c r="J38" s="19" t="n">
+        <v/>
+      </c>
       <c r="K38" s="20" t="inlineStr"/>
     </row>
     <row r="39" ht="104.4" customHeight="1" s="21">
@@ -3050,8 +3168,12 @@
 -RAN CABLE 수량 누락</t>
         </is>
       </c>
-      <c r="I39" s="11" t="inlineStr"/>
-      <c r="J39" s="19" t="inlineStr"/>
+      <c r="I39" s="11" t="n">
+        <v/>
+      </c>
+      <c r="J39" s="19" t="n">
+        <v/>
+      </c>
       <c r="K39" s="20" t="inlineStr"/>
     </row>
     <row r="40" ht="139.2" customHeight="1" s="21">
@@ -3096,7 +3218,9 @@
           <t>1~05 입고요청</t>
         </is>
       </c>
-      <c r="J40" s="19" t="inlineStr"/>
+      <c r="J40" s="19" t="n">
+        <v/>
+      </c>
       <c r="K40" s="20" t="inlineStr"/>
     </row>
     <row r="41" ht="87" customHeight="1" s="21">
@@ -3135,8 +3259,12 @@
 -전장팀 요청 버튼 조작을 위한 REAR MONITER COVER의 여닫이 COVER 추가</t>
         </is>
       </c>
-      <c r="I41" s="11" t="inlineStr"/>
-      <c r="J41" s="19" t="inlineStr"/>
+      <c r="I41" s="11" t="n">
+        <v/>
+      </c>
+      <c r="J41" s="19" t="n">
+        <v/>
+      </c>
       <c r="K41" s="20" t="inlineStr"/>
     </row>
     <row r="42" ht="34.8" customHeight="1" s="21">
@@ -3173,8 +3301,12 @@
           <t xml:space="preserve"> -SLH1 SOCAMM 전용 T-TRAY,MASK, PRECISER 등록 및 2호기 적용파트 발주 건(업체 JIG 지정 요청)</t>
         </is>
       </c>
-      <c r="I42" s="11" t="inlineStr"/>
-      <c r="J42" s="19" t="inlineStr"/>
+      <c r="I42" s="11" t="n">
+        <v/>
+      </c>
+      <c r="J42" s="19" t="n">
+        <v/>
+      </c>
       <c r="K42" s="20" t="inlineStr"/>
     </row>
     <row r="43" ht="139.2" customHeight="1" s="21">
@@ -3215,8 +3347,12 @@
 ㄴ항목 11,13 수량 삭제 12,14 수량 변경 및 추가분 발주(SLH1-PP-251230-11 발주분 외 추가 발주) </t>
         </is>
       </c>
-      <c r="I43" s="11" t="inlineStr"/>
-      <c r="J43" s="19" t="inlineStr"/>
+      <c r="I43" s="11" t="n">
+        <v/>
+      </c>
+      <c r="J43" s="19" t="n">
+        <v/>
+      </c>
       <c r="K43" s="20" t="inlineStr"/>
     </row>
     <row r="44">
@@ -3253,8 +3389,12 @@
           <t>도면 높이 치수 공차 추가 BOM UPDATE</t>
         </is>
       </c>
-      <c r="I44" s="11" t="inlineStr"/>
-      <c r="J44" s="19" t="inlineStr"/>
+      <c r="I44" s="11" t="n">
+        <v/>
+      </c>
+      <c r="J44" s="19" t="n">
+        <v/>
+      </c>
       <c r="K44" s="20" t="inlineStr"/>
     </row>
     <row r="45">
@@ -3296,7 +3436,9 @@
           <t>1~08 입고요청</t>
         </is>
       </c>
-      <c r="J45" s="19" t="inlineStr"/>
+      <c r="J45" s="19" t="n">
+        <v/>
+      </c>
       <c r="K45" s="20" t="inlineStr"/>
     </row>
     <row r="46">
@@ -3333,8 +3475,12 @@
           <t>제조팀 요청 마운트 탭 추가</t>
         </is>
       </c>
-      <c r="I46" s="11" t="inlineStr"/>
-      <c r="J46" s="19" t="inlineStr"/>
+      <c r="I46" s="11" t="n">
+        <v/>
+      </c>
+      <c r="J46" s="19" t="n">
+        <v/>
+      </c>
       <c r="K46" s="20" t="inlineStr"/>
     </row>
     <row r="47">
@@ -3371,8 +3517,12 @@
           <t>VISION BRK 변경</t>
         </is>
       </c>
-      <c r="I47" s="11" t="inlineStr"/>
-      <c r="J47" s="19" t="inlineStr"/>
+      <c r="I47" s="11" t="n">
+        <v/>
+      </c>
+      <c r="J47" s="19" t="n">
+        <v/>
+      </c>
       <c r="K47" s="20" t="inlineStr"/>
     </row>
     <row r="48" ht="34.8" customHeight="1" s="21">
@@ -3409,8 +3559,12 @@
           <t>FRAME 고정용 ANCHOR BRK 추가</t>
         </is>
       </c>
-      <c r="I48" s="11" t="inlineStr"/>
-      <c r="J48" s="19" t="inlineStr"/>
+      <c r="I48" s="11" t="n">
+        <v/>
+      </c>
+      <c r="J48" s="19" t="n">
+        <v/>
+      </c>
       <c r="K48" s="20" t="inlineStr"/>
     </row>
     <row r="49" ht="34.8" customHeight="1" s="21">
@@ -3448,8 +3602,12 @@
 -EMS 황색 명판 삭제 요청(고객사 요청)</t>
         </is>
       </c>
-      <c r="I49" s="11" t="inlineStr"/>
-      <c r="J49" s="19" t="inlineStr"/>
+      <c r="I49" s="11" t="n">
+        <v/>
+      </c>
+      <c r="J49" s="19" t="n">
+        <v/>
+      </c>
       <c r="K49" s="20" t="inlineStr"/>
     </row>
     <row r="50" ht="69.59999999999999" customHeight="1" s="21">
@@ -3488,8 +3646,12 @@
 -AF-BM 으로 변경하여 적용 예정</t>
         </is>
       </c>
-      <c r="I50" s="11" t="inlineStr"/>
-      <c r="J50" s="19" t="inlineStr"/>
+      <c r="I50" s="11" t="n">
+        <v/>
+      </c>
+      <c r="J50" s="19" t="n">
+        <v/>
+      </c>
       <c r="K50" s="20" t="inlineStr"/>
     </row>
     <row r="51" ht="34.8" customHeight="1" s="21">
@@ -3526,8 +3688,12 @@
           <t>SLH1 SOCAMM INSC0-IB-06-0 : AD32CM INSERT 부품과 공용 사용/기존 도면 참조</t>
         </is>
       </c>
-      <c r="I51" s="11" t="inlineStr"/>
-      <c r="J51" s="19" t="inlineStr"/>
+      <c r="I51" s="11" t="n">
+        <v/>
+      </c>
+      <c r="J51" s="19" t="n">
+        <v/>
+      </c>
       <c r="K51" s="20" t="inlineStr"/>
     </row>
     <row r="52">
@@ -3564,8 +3730,12 @@
           <t>LED 설치 BRK 추가</t>
         </is>
       </c>
-      <c r="I52" s="11" t="inlineStr"/>
-      <c r="J52" s="19" t="inlineStr"/>
+      <c r="I52" s="11" t="n">
+        <v/>
+      </c>
+      <c r="J52" s="19" t="n">
+        <v/>
+      </c>
       <c r="K52" s="20" t="inlineStr"/>
     </row>
     <row r="53">
@@ -3602,8 +3772,12 @@
           <t>TRAY GUIDE BLOCK 길이 다르게 수정하여 TEST 진행</t>
         </is>
       </c>
-      <c r="I53" s="11" t="inlineStr"/>
-      <c r="J53" s="19" t="inlineStr"/>
+      <c r="I53" s="11" t="n">
+        <v/>
+      </c>
+      <c r="J53" s="19" t="n">
+        <v/>
+      </c>
       <c r="K53" s="20" t="inlineStr"/>
     </row>
     <row r="54" ht="139.2" customHeight="1" s="21">
@@ -3646,8 +3820,12 @@
 -신규 블록 추가로 인한 홀 추가</t>
         </is>
       </c>
-      <c r="I54" s="11" t="inlineStr"/>
-      <c r="J54" s="19" t="inlineStr"/>
+      <c r="I54" s="11" t="n">
+        <v/>
+      </c>
+      <c r="J54" s="19" t="n">
+        <v/>
+      </c>
       <c r="K54" s="20" t="inlineStr">
         <is>
           <t>\\192.168.0.100\500 생산\550 국내CS\ECN&amp;STN\SLH1-PP-260112-01(5건).pdf</t>
@@ -3690,8 +3868,12 @@
 -BUSH BLOCK TAP 양면 가공 추가</t>
         </is>
       </c>
-      <c r="I55" s="11" t="inlineStr"/>
-      <c r="J55" s="19" t="inlineStr"/>
+      <c r="I55" s="11" t="n">
+        <v/>
+      </c>
+      <c r="J55" s="19" t="n">
+        <v/>
+      </c>
       <c r="K55" s="20" t="inlineStr">
         <is>
           <t>\\192.168.0.100\500 생산\550 국내CS\ECN&amp;STN\SLH1-PP-260115-01(Tary Flow 상단 LED 설치 Tap 누락으로 추가).pdf</t>
@@ -3732,8 +3914,12 @@
           <t>장비 제작 간 케이블 하네스 불합리 및 누락 케이블 추가 업데이트 및 구매</t>
         </is>
       </c>
-      <c r="I56" s="11" t="inlineStr"/>
-      <c r="J56" s="19" t="inlineStr"/>
+      <c r="I56" s="11" t="n">
+        <v/>
+      </c>
+      <c r="J56" s="19" t="n">
+        <v/>
+      </c>
       <c r="K56" s="20" t="inlineStr"/>
     </row>
     <row r="57" ht="52.2" customHeight="1" s="21">
@@ -3771,8 +3957,12 @@
 -제조팀 요청 간섭 및 조립 편의성을 위한 홀 타입 변경</t>
         </is>
       </c>
-      <c r="I57" s="11" t="inlineStr"/>
-      <c r="J57" s="19" t="inlineStr"/>
+      <c r="I57" s="11" t="n">
+        <v/>
+      </c>
+      <c r="J57" s="19" t="n">
+        <v/>
+      </c>
       <c r="K57" s="20" t="inlineStr">
         <is>
           <t>\\192.168.0.100\500 생산\550 국내CS\ECN&amp;STN\SLH1-PP-260119-01(SetPlate Indigator Cover 탭장공,홀 탭 변경,Size 변경).pdf</t>
@@ -3813,8 +4003,12 @@
           <t>SOCAMM HAND VISION BRK 변경으로 인한 설계 변경</t>
         </is>
       </c>
-      <c r="I58" s="11" t="inlineStr"/>
-      <c r="J58" s="19" t="inlineStr"/>
+      <c r="I58" s="11" t="n">
+        <v/>
+      </c>
+      <c r="J58" s="19" t="n">
+        <v/>
+      </c>
       <c r="K58" s="20" t="inlineStr"/>
     </row>
     <row r="59" ht="87" customHeight="1" s="21">
@@ -3853,8 +4047,12 @@
 -신규 브라켓 추가로 인한 블록 TAP 추가</t>
         </is>
       </c>
-      <c r="I59" s="11" t="inlineStr"/>
-      <c r="J59" s="19" t="inlineStr"/>
+      <c r="I59" s="11" t="n">
+        <v/>
+      </c>
+      <c r="J59" s="19" t="n">
+        <v/>
+      </c>
       <c r="K59" s="20" t="inlineStr">
         <is>
           <t>\\192.168.0.100\500 생산\550 국내CS\ECN&amp;STN\SLH1-PP-260121-01(Align Guide 1 하단 Block 추가).pdf</t>
@@ -3895,8 +4093,12 @@
           <t>장비 제작 간 케이블 하네스 불합리 및 누락 케이블 추가 업데이트</t>
         </is>
       </c>
-      <c r="I60" s="11" t="inlineStr"/>
-      <c r="J60" s="19" t="inlineStr"/>
+      <c r="I60" s="11" t="n">
+        <v/>
+      </c>
+      <c r="J60" s="19" t="n">
+        <v/>
+      </c>
       <c r="K60" s="20" t="inlineStr"/>
     </row>
     <row r="61" ht="34.8" customHeight="1" s="21">
@@ -3933,8 +4135,12 @@
           <t>장비 제작 간 케이블 하네스 불합리 및 누락 케이블 추가 업데이트</t>
         </is>
       </c>
-      <c r="I61" s="11" t="inlineStr"/>
-      <c r="J61" s="19" t="inlineStr"/>
+      <c r="I61" s="11" t="n">
+        <v/>
+      </c>
+      <c r="J61" s="19" t="n">
+        <v/>
+      </c>
       <c r="K61" s="20" t="inlineStr"/>
     </row>
     <row r="62">
@@ -3976,7 +4182,9 @@
           <t>1~27 입고요청</t>
         </is>
       </c>
-      <c r="J62" s="19" t="inlineStr"/>
+      <c r="J62" s="19" t="n">
+        <v/>
+      </c>
       <c r="K62" s="20" t="inlineStr">
         <is>
           <t>\\192.168.0.100\500 생산\550 국내CS\ECN&amp;STN\None.pdf</t>
@@ -4018,8 +4226,12 @@
 -ALIGN SHAFT 위치 조절 불가로 인한 블록 형상 변경</t>
         </is>
       </c>
-      <c r="I63" s="11" t="inlineStr"/>
-      <c r="J63" s="19" t="inlineStr"/>
+      <c r="I63" s="11" t="n">
+        <v/>
+      </c>
+      <c r="J63" s="19" t="n">
+        <v/>
+      </c>
       <c r="K63" s="20" t="inlineStr">
         <is>
           <t>\\192.168.0.100\500 생산\550 국내CS\ECN&amp;STN\SLH1-PP-260123-01(낙수방지를 위한 TOP Cover 추가).pdf</t>
@@ -4060,8 +4272,12 @@
           <t>고객사 요구사항에 대응되는 PAD로 변경(마크리스 특수코팅 추가)</t>
         </is>
       </c>
-      <c r="I64" s="11" t="inlineStr"/>
-      <c r="J64" s="19" t="inlineStr"/>
+      <c r="I64" s="11" t="n">
+        <v/>
+      </c>
+      <c r="J64" s="19" t="n">
+        <v/>
+      </c>
       <c r="K64" s="20" t="inlineStr">
         <is>
           <t>\\192.168.0.100\500 생산\550 국내CS\ECN&amp;STN\SLH1-PP-260127-01(Hand Picker EDS 부적격으로 마크리스 특수코팅추가).pdf</t>
@@ -4105,8 +4321,12 @@
 -고객사 요청 재질 변경</t>
         </is>
       </c>
-      <c r="I65" s="11" t="inlineStr"/>
-      <c r="J65" s="19" t="inlineStr"/>
+      <c r="I65" s="11" t="n">
+        <v/>
+      </c>
+      <c r="J65" s="19" t="n">
+        <v/>
+      </c>
       <c r="K65" s="20" t="inlineStr">
         <is>
           <t>\\192.168.0.100\500 생산\550 국내CS\ECN&amp;STN\SLH1-PP-260126-01(Rear Cover Bolt와 덕트 간섭으로 상대물에 Tap추가).pdf</t>
@@ -4149,8 +4369,12 @@
 -케이블과 간섭으로 인한 가공 추가</t>
         </is>
       </c>
-      <c r="I66" s="11" t="inlineStr"/>
-      <c r="J66" s="19" t="inlineStr"/>
+      <c r="I66" s="11" t="n">
+        <v/>
+      </c>
+      <c r="J66" s="19" t="n">
+        <v/>
+      </c>
       <c r="K66" s="20" t="inlineStr">
         <is>
           <t>\\192.168.0.100\500 생산\550 국내CS\ECN&amp;STN\SLH1-PP-260128-01(Transfer Support Shaft 크기 축소).pdf</t>
@@ -4192,8 +4416,12 @@
 -TRAY 진입 불가로 인한 가공품 두께 변경</t>
         </is>
       </c>
-      <c r="I67" s="11" t="inlineStr"/>
-      <c r="J67" s="19" t="inlineStr"/>
+      <c r="I67" s="11" t="n">
+        <v/>
+      </c>
+      <c r="J67" s="19" t="n">
+        <v/>
+      </c>
       <c r="K67" s="20" t="inlineStr">
         <is>
           <t>\\192.168.0.100\500 생산\550 국내CS\ECN&amp;STN\SLH1-PP-260127-02(Flow Rail 타가이드 두께변경）.pdf</t>
@@ -4236,8 +4464,12 @@
 -하위 파트 REV 변경에 따른 REV 변경, 조립 위치 변경</t>
         </is>
       </c>
-      <c r="I68" s="11" t="inlineStr"/>
-      <c r="J68" s="19" t="inlineStr"/>
+      <c r="I68" s="11" t="n">
+        <v/>
+      </c>
+      <c r="J68" s="19" t="n">
+        <v/>
+      </c>
       <c r="K68" s="20" t="inlineStr"/>
     </row>
     <row r="69" ht="156.6" customHeight="1" s="21">
@@ -4278,8 +4510,12 @@
 -SPRING 결합 위치 변경 및 OPEN 각도 조정을 위한 형상 변경</t>
         </is>
       </c>
-      <c r="I69" s="11" t="inlineStr"/>
-      <c r="J69" s="19" t="inlineStr"/>
+      <c r="I69" s="11" t="n">
+        <v/>
+      </c>
+      <c r="J69" s="19" t="n">
+        <v/>
+      </c>
       <c r="K69" s="20" t="inlineStr"/>
     </row>
     <row r="70" ht="52.2" customHeight="1" s="21">
@@ -4317,8 +4553,12 @@
 -가공업체 요청 라운드 값 변경, 표면 저항값 삭제</t>
         </is>
       </c>
-      <c r="I70" s="11" t="inlineStr"/>
-      <c r="J70" s="19" t="inlineStr"/>
+      <c r="I70" s="11" t="n">
+        <v/>
+      </c>
+      <c r="J70" s="19" t="n">
+        <v/>
+      </c>
       <c r="K70" s="20" t="inlineStr">
         <is>
           <t>\\192.168.0.100\500 생산\550 국내CS\ECN&amp;STN\ECN SLH1-TP-260122-01（Socamm BCR Block 추가）.pdf</t>
@@ -4361,8 +4601,12 @@
 -STACKER MANUAL PORT 롤러 간섭으로 인한 가공 추가</t>
         </is>
       </c>
-      <c r="I71" s="11" t="inlineStr"/>
-      <c r="J71" s="19" t="inlineStr"/>
+      <c r="I71" s="11" t="n">
+        <v/>
+      </c>
+      <c r="J71" s="19" t="n">
+        <v/>
+      </c>
       <c r="K71" s="20" t="inlineStr">
         <is>
           <t>\\192.168.0.100\500 생산\550 국내CS\ECN&amp;STN\SLH1-PP-260205-01(Reject Stacker Align BRK 장공크기 조정 및 불필요 장공 삭제).pdf</t>
@@ -4409,8 +4653,12 @@
 -구매팀 요청 CCTV 세트화 해제로 인한 추가 발주</t>
         </is>
       </c>
-      <c r="I72" s="11" t="inlineStr"/>
-      <c r="J72" s="19" t="inlineStr"/>
+      <c r="I72" s="11" t="n">
+        <v/>
+      </c>
+      <c r="J72" s="19" t="n">
+        <v/>
+      </c>
       <c r="K72" s="20" t="inlineStr">
         <is>
           <t>\\192.168.0.100\500 생산\550 국내CS\ECN&amp;STN\SLH1-PP-260210-01(RDIMM Stacker Align BRK).pdf</t>
@@ -4455,8 +4703,12 @@
 -SHAFT 사이의 틈이 좁아 휨 이슈로 인한 가공 추가</t>
         </is>
       </c>
-      <c r="I73" s="11" t="inlineStr"/>
-      <c r="J73" s="19" t="inlineStr"/>
+      <c r="I73" s="11" t="n">
+        <v/>
+      </c>
+      <c r="J73" s="19" t="n">
+        <v/>
+      </c>
       <c r="K73" s="20" t="inlineStr">
         <is>
           <t>\\192.168.0.100\500 생산\550 국내CS\ECN&amp;STN\SLH1-PP-260204-01(Transfer Tray Check Sensor 고정 BRK 길이 변경, 탭변경).pdf</t>
@@ -4497,8 +4749,12 @@
           <t>BOM 수량 MISS 건 BOM UPDATE</t>
         </is>
       </c>
-      <c r="I74" s="11" t="inlineStr"/>
-      <c r="J74" s="19" t="inlineStr"/>
+      <c r="I74" s="11" t="n">
+        <v/>
+      </c>
+      <c r="J74" s="19" t="n">
+        <v/>
+      </c>
       <c r="K74" s="20" t="inlineStr"/>
     </row>
     <row r="75">
@@ -4535,8 +4791,12 @@
           <t>고객사 요청 판넬 모서리 보호대 추가</t>
         </is>
       </c>
-      <c r="I75" s="11" t="inlineStr"/>
-      <c r="J75" s="19" t="inlineStr"/>
+      <c r="I75" s="11" t="n">
+        <v/>
+      </c>
+      <c r="J75" s="19" t="n">
+        <v/>
+      </c>
       <c r="K75" s="20" t="inlineStr">
         <is>
           <t>\\192.168.0.100\500 생산\550 국내CS\ECN&amp;STN\ECN SLH1-PP-260219-01(Conveyor Inverter 장착Pannel 모서리가드 추가).pdf</t>
@@ -4577,8 +4837,12 @@
           <t>CCTV 브라켓 신규 추가</t>
         </is>
       </c>
-      <c r="I76" s="11" t="inlineStr"/>
-      <c r="J76" s="19" t="inlineStr"/>
+      <c r="I76" s="11" t="n">
+        <v/>
+      </c>
+      <c r="J76" s="19" t="n">
+        <v/>
+      </c>
       <c r="K76" s="20" t="inlineStr">
         <is>
           <t>\\192.168.0.100\500 생산\550 국내CS\ECN&amp;STN\ECN SLH1-PP-260219-02(CCTV BRK 신규추가).pdf</t>
@@ -4619,8 +4883,12 @@
           <t>장비제작 간 케이블 하네스 불합리 및 누락 케이블 추가 업데이트</t>
         </is>
       </c>
-      <c r="I77" s="11" t="inlineStr"/>
-      <c r="J77" s="19" t="inlineStr"/>
+      <c r="I77" s="11" t="n">
+        <v/>
+      </c>
+      <c r="J77" s="19" t="n">
+        <v/>
+      </c>
       <c r="K77" s="20" t="inlineStr">
         <is>
           <t>\\192.168.0.100\500 생산\550 국내CS\ECN&amp;STN\None.pdf</t>
@@ -4665,8 +4933,12 @@
 -신규 브라켓 추가로 인한 기존 브라켓 및 ROLLER 4EA 폐기</t>
         </is>
       </c>
-      <c r="I78" s="11" t="inlineStr"/>
-      <c r="J78" s="19" t="inlineStr"/>
+      <c r="I78" s="11" t="n">
+        <v/>
+      </c>
+      <c r="J78" s="19" t="n">
+        <v/>
+      </c>
       <c r="K78" s="20" t="inlineStr">
         <is>
           <t>\\192.168.0.100\500 생산\550 국내CS\ECN&amp;STN\ECN SLH1-PP-260225-01(Tray Flow Preciser Insert Pitch Fitting 추가).pdf</t>
@@ -4708,8 +4980,12 @@
 -설계 MISS로 인한 변경 진행(긴급, 고객 검수 다음주 진행)</t>
         </is>
       </c>
-      <c r="I79" s="11" t="inlineStr"/>
-      <c r="J79" s="19" t="inlineStr"/>
+      <c r="I79" s="11" t="n">
+        <v/>
+      </c>
+      <c r="J79" s="19" t="n">
+        <v/>
+      </c>
       <c r="K79" s="20" t="inlineStr"/>
     </row>
     <row r="80" ht="52.2" customHeight="1" s="21">
@@ -4746,8 +5022,12 @@
           <t>고객사 요청 SOCAMM HAND GRIP의 공압을 최소로 가져가기 위한 브라켓 설계 변경 및 SPACER, AIR FILTER 추가</t>
         </is>
       </c>
-      <c r="I80" s="11" t="inlineStr"/>
-      <c r="J80" s="19" t="inlineStr"/>
+      <c r="I80" s="11" t="n">
+        <v/>
+      </c>
+      <c r="J80" s="19" t="n">
+        <v/>
+      </c>
       <c r="K80" s="20" t="inlineStr">
         <is>
           <t>\\192.168.0.100\500 생산\550 국내CS\ECN&amp;STN\SLH1-PP-260305-01(SOCAMM HAND 공압 변경 및 필터 추가).pdf</t>
@@ -4791,8 +5071,14 @@
 -SOCAMM PRECISER CONVERSION 체크 브러캣 추가</t>
         </is>
       </c>
-      <c r="I81" s="11" t="inlineStr"/>
-      <c r="J81" s="19" t="inlineStr"/>
+      <c r="I81" s="11" t="n">
+        <v/>
+      </c>
+      <c r="J81" s="19" t="inlineStr">
+        <is>
+          <t>완료.</t>
+        </is>
+      </c>
       <c r="K81" s="20" t="inlineStr">
         <is>
           <t>\\192.168.0.100\500 생산\550 국내CS\ECN&amp;STN\ECN SLH1-PP-260227-01(후면부 Regulator Sensor 위치 개선).pdf</t>
@@ -4839,7 +5125,9 @@
 -SOCAMM STACKER ALIGN SHAFT 처짐으로 인한 BRACKET,LM GUIDE 추가</t>
         </is>
       </c>
-      <c r="I82" s="11" t="inlineStr"/>
+      <c r="I82" s="11" t="n">
+        <v/>
+      </c>
       <c r="J82" s="19" t="inlineStr">
         <is>
           <t>횡전개 완료.</t>
@@ -4889,8 +5177,12 @@
 -상위 ASSY 도면 업데이트</t>
         </is>
       </c>
-      <c r="I83" s="11" t="inlineStr"/>
-      <c r="J83" s="19" t="inlineStr"/>
+      <c r="I83" s="11" t="n">
+        <v/>
+      </c>
+      <c r="J83" s="19" t="n">
+        <v/>
+      </c>
       <c r="K83" s="20" t="inlineStr"/>
     </row>
     <row r="84" ht="69.59999999999999" customHeight="1" s="21">
@@ -4928,8 +5220,12 @@
 -STACKER REJECK BOTTOM 컨베이어 STOP을 위한 센서 홀 없음</t>
         </is>
       </c>
-      <c r="I84" s="11" t="inlineStr"/>
-      <c r="J84" s="19" t="inlineStr"/>
+      <c r="I84" s="11" t="n">
+        <v/>
+      </c>
+      <c r="J84" s="19" t="n">
+        <v/>
+      </c>
       <c r="K84" s="20" t="inlineStr"/>
     </row>
   </sheetData>

--- a/data/ECN/ECN_STN_Master(SLH1).xlsx
+++ b/data/ECN/ECN_STN_Master(SLH1).xlsx
@@ -1585,8 +1585,10 @@
           <t xml:space="preserve">11-17일 입고 요청 </t>
         </is>
       </c>
-      <c r="J4" s="19" t="n">
-        <v/>
+      <c r="J4" s="19" t="inlineStr">
+        <is>
+          <t>완료.</t>
+        </is>
       </c>
       <c r="K4" s="20" t="inlineStr"/>
     </row>
@@ -1642,8 +1644,10 @@
           <t>11~26 입고 요청</t>
         </is>
       </c>
-      <c r="J5" s="19" t="n">
-        <v/>
+      <c r="J5" s="19" t="inlineStr">
+        <is>
+          <t>완료.</t>
+        </is>
       </c>
       <c r="K5" s="20" t="inlineStr"/>
     </row>
@@ -1687,8 +1691,10 @@
           <t>11~28 입고 요청</t>
         </is>
       </c>
-      <c r="J6" s="19" t="n">
-        <v/>
+      <c r="J6" s="19" t="inlineStr">
+        <is>
+          <t>완료.</t>
+        </is>
       </c>
       <c r="K6" s="20" t="inlineStr"/>
     </row>
@@ -1727,8 +1733,10 @@
           <t>11~28일 입고 요청</t>
         </is>
       </c>
-      <c r="J7" s="19" t="n">
-        <v/>
+      <c r="J7" s="19" t="inlineStr">
+        <is>
+          <t>완료.</t>
+        </is>
       </c>
       <c r="K7" s="20" t="inlineStr"/>
     </row>
@@ -1765,8 +1773,10 @@
       <c r="I8" s="11" t="n">
         <v/>
       </c>
-      <c r="J8" s="19" t="n">
-        <v/>
+      <c r="J8" s="19" t="inlineStr">
+        <is>
+          <t>완료.</t>
+        </is>
       </c>
       <c r="K8" s="20" t="inlineStr"/>
     </row>
@@ -1811,8 +1821,10 @@
       <c r="I9" s="11" t="n">
         <v/>
       </c>
-      <c r="J9" s="19" t="n">
-        <v/>
+      <c r="J9" s="19" t="inlineStr">
+        <is>
+          <t>완료.</t>
+        </is>
       </c>
       <c r="K9" s="20" t="inlineStr"/>
     </row>
@@ -1856,8 +1868,10 @@
           <t>11~28일 입고 요청</t>
         </is>
       </c>
-      <c r="J10" s="19" t="n">
-        <v/>
+      <c r="J10" s="19" t="inlineStr">
+        <is>
+          <t>완료.</t>
+        </is>
       </c>
       <c r="K10" s="20" t="inlineStr"/>
     </row>
@@ -1899,8 +1913,10 @@
       <c r="I11" s="11" t="n">
         <v/>
       </c>
-      <c r="J11" s="19" t="n">
-        <v/>
+      <c r="J11" s="19" t="inlineStr">
+        <is>
+          <t>완료.</t>
+        </is>
       </c>
       <c r="K11" s="20" t="inlineStr"/>
     </row>
@@ -1942,8 +1958,10 @@
       <c r="I12" s="11" t="n">
         <v/>
       </c>
-      <c r="J12" s="19" t="n">
-        <v/>
+      <c r="J12" s="19" t="inlineStr">
+        <is>
+          <t>완료.</t>
+        </is>
       </c>
       <c r="K12" s="20" t="inlineStr"/>
     </row>
@@ -1986,8 +2004,10 @@
           <t>12~01일 입고 요청</t>
         </is>
       </c>
-      <c r="J13" s="19" t="n">
-        <v/>
+      <c r="J13" s="19" t="inlineStr">
+        <is>
+          <t>완료.</t>
+        </is>
       </c>
       <c r="K13" s="20" t="inlineStr"/>
     </row>
@@ -2034,8 +2054,10 @@
           <t>12~2일 입고 요청</t>
         </is>
       </c>
-      <c r="J14" s="19" t="n">
-        <v/>
+      <c r="J14" s="19" t="inlineStr">
+        <is>
+          <t>완료.</t>
+        </is>
       </c>
       <c r="K14" s="20" t="inlineStr"/>
     </row>
@@ -2076,8 +2098,10 @@
       <c r="I15" s="11" t="n">
         <v/>
       </c>
-      <c r="J15" s="19" t="n">
-        <v/>
+      <c r="J15" s="19" t="inlineStr">
+        <is>
+          <t>완료.</t>
+        </is>
       </c>
       <c r="K15" s="20" t="inlineStr"/>
     </row>
@@ -2118,8 +2142,10 @@
       <c r="I16" s="11" t="n">
         <v/>
       </c>
-      <c r="J16" s="19" t="n">
-        <v/>
+      <c r="J16" s="19" t="inlineStr">
+        <is>
+          <t>완료.</t>
+        </is>
       </c>
       <c r="K16" s="20" t="inlineStr"/>
     </row>
@@ -2168,8 +2194,10 @@
           <t>12~5일 입고 요청</t>
         </is>
       </c>
-      <c r="J17" s="19" t="n">
-        <v/>
+      <c r="J17" s="19" t="inlineStr">
+        <is>
+          <t>완료.</t>
+        </is>
       </c>
       <c r="K17" s="20" t="inlineStr"/>
     </row>
@@ -2216,8 +2244,10 @@
           <t>12~4일 입고 요청</t>
         </is>
       </c>
-      <c r="J18" s="19" t="n">
-        <v/>
+      <c r="J18" s="19" t="inlineStr">
+        <is>
+          <t>완료.</t>
+        </is>
       </c>
       <c r="K18" s="20" t="inlineStr"/>
     </row>
@@ -2263,8 +2293,10 @@
       <c r="I19" s="11" t="n">
         <v/>
       </c>
-      <c r="J19" s="19" t="n">
-        <v/>
+      <c r="J19" s="19" t="inlineStr">
+        <is>
+          <t>완료.</t>
+        </is>
       </c>
       <c r="K19" s="20" t="inlineStr"/>
     </row>
@@ -2313,8 +2345,10 @@
           <t>12~9일 입고요청</t>
         </is>
       </c>
-      <c r="J20" s="19" t="n">
-        <v/>
+      <c r="J20" s="19" t="inlineStr">
+        <is>
+          <t>완료.</t>
+        </is>
       </c>
       <c r="K20" s="20" t="inlineStr"/>
     </row>
@@ -2361,8 +2395,10 @@
           <t>12~12일 입고요청</t>
         </is>
       </c>
-      <c r="J21" s="19" t="n">
-        <v/>
+      <c r="J21" s="19" t="inlineStr">
+        <is>
+          <t>완료.</t>
+        </is>
       </c>
       <c r="K21" s="20" t="inlineStr"/>
     </row>
@@ -2408,8 +2444,10 @@
       <c r="I22" s="11" t="n">
         <v/>
       </c>
-      <c r="J22" s="19" t="n">
-        <v/>
+      <c r="J22" s="19" t="inlineStr">
+        <is>
+          <t>완료.</t>
+        </is>
       </c>
       <c r="K22" s="20" t="inlineStr"/>
     </row>
@@ -2454,8 +2492,10 @@
       <c r="I23" s="11" t="n">
         <v/>
       </c>
-      <c r="J23" s="19" t="n">
-        <v/>
+      <c r="J23" s="19" t="inlineStr">
+        <is>
+          <t>완료.</t>
+        </is>
       </c>
       <c r="K23" s="20" t="inlineStr"/>
     </row>
@@ -2498,8 +2538,10 @@
       <c r="I24" s="11" t="n">
         <v/>
       </c>
-      <c r="J24" s="19" t="n">
-        <v/>
+      <c r="J24" s="19" t="inlineStr">
+        <is>
+          <t>완료.</t>
+        </is>
       </c>
       <c r="K24" s="20" t="inlineStr"/>
     </row>
@@ -2543,8 +2585,10 @@
       <c r="I25" s="11" t="n">
         <v/>
       </c>
-      <c r="J25" s="19" t="n">
-        <v/>
+      <c r="J25" s="19" t="inlineStr">
+        <is>
+          <t>완료.</t>
+        </is>
       </c>
       <c r="K25" s="20" t="inlineStr"/>
     </row>
@@ -2588,8 +2632,10 @@
       <c r="I26" s="11" t="n">
         <v/>
       </c>
-      <c r="J26" s="19" t="n">
-        <v/>
+      <c r="J26" s="19" t="inlineStr">
+        <is>
+          <t>완료.</t>
+        </is>
       </c>
       <c r="K26" s="20" t="inlineStr"/>
     </row>
@@ -2639,8 +2685,10 @@
       <c r="I27" s="11" t="n">
         <v/>
       </c>
-      <c r="J27" s="19" t="n">
-        <v/>
+      <c r="J27" s="19" t="inlineStr">
+        <is>
+          <t>완료.</t>
+        </is>
       </c>
       <c r="K27" s="20" t="inlineStr"/>
     </row>
@@ -2682,8 +2730,10 @@
       <c r="I28" s="11" t="n">
         <v/>
       </c>
-      <c r="J28" s="19" t="n">
-        <v/>
+      <c r="J28" s="19" t="inlineStr">
+        <is>
+          <t>완료.</t>
+        </is>
       </c>
       <c r="K28" s="20" t="inlineStr"/>
     </row>
@@ -2724,8 +2774,10 @@
       <c r="I29" s="11" t="n">
         <v/>
       </c>
-      <c r="J29" s="19" t="n">
-        <v/>
+      <c r="J29" s="19" t="inlineStr">
+        <is>
+          <t>완료.</t>
+        </is>
       </c>
       <c r="K29" s="20" t="inlineStr"/>
     </row>
@@ -2766,8 +2818,10 @@
       <c r="I30" s="11" t="n">
         <v/>
       </c>
-      <c r="J30" s="19" t="n">
-        <v/>
+      <c r="J30" s="19" t="inlineStr">
+        <is>
+          <t>완료.</t>
+        </is>
       </c>
       <c r="K30" s="20" t="inlineStr"/>
     </row>
@@ -2812,8 +2866,10 @@
       <c r="I31" s="11" t="n">
         <v/>
       </c>
-      <c r="J31" s="19" t="n">
-        <v/>
+      <c r="J31" s="19" t="inlineStr">
+        <is>
+          <t>완료.</t>
+        </is>
       </c>
       <c r="K31" s="20" t="inlineStr"/>
     </row>
@@ -2854,8 +2910,10 @@
       <c r="I32" s="11" t="n">
         <v/>
       </c>
-      <c r="J32" s="19" t="n">
-        <v/>
+      <c r="J32" s="19" t="inlineStr">
+        <is>
+          <t>완료.</t>
+        </is>
       </c>
       <c r="K32" s="20" t="inlineStr"/>
     </row>
@@ -2899,8 +2957,10 @@
       <c r="I33" s="11" t="n">
         <v/>
       </c>
-      <c r="J33" s="19" t="n">
-        <v/>
+      <c r="J33" s="19" t="inlineStr">
+        <is>
+          <t>완료.</t>
+        </is>
       </c>
       <c r="K33" s="20" t="inlineStr"/>
     </row>
@@ -2942,8 +3002,10 @@
       <c r="I34" s="11" t="n">
         <v/>
       </c>
-      <c r="J34" s="19" t="n">
-        <v/>
+      <c r="J34" s="19" t="inlineStr">
+        <is>
+          <t>완료.</t>
+        </is>
       </c>
       <c r="K34" s="20" t="inlineStr"/>
     </row>
@@ -2991,8 +3053,10 @@
       <c r="I35" s="11" t="n">
         <v/>
       </c>
-      <c r="J35" s="19" t="n">
-        <v/>
+      <c r="J35" s="19" t="inlineStr">
+        <is>
+          <t>완료.</t>
+        </is>
       </c>
       <c r="K35" s="20" t="inlineStr"/>
     </row>
@@ -3037,8 +3101,10 @@
       <c r="I36" s="11" t="n">
         <v/>
       </c>
-      <c r="J36" s="19" t="n">
-        <v/>
+      <c r="J36" s="19" t="inlineStr">
+        <is>
+          <t>완료.</t>
+        </is>
       </c>
       <c r="K36" s="20" t="inlineStr"/>
     </row>
@@ -3082,8 +3148,10 @@
       <c r="I37" s="11" t="n">
         <v/>
       </c>
-      <c r="J37" s="19" t="n">
-        <v/>
+      <c r="J37" s="19" t="inlineStr">
+        <is>
+          <t>완료.</t>
+        </is>
       </c>
       <c r="K37" s="20" t="inlineStr"/>
     </row>
@@ -3126,8 +3194,10 @@
       <c r="I38" s="11" t="n">
         <v/>
       </c>
-      <c r="J38" s="19" t="n">
-        <v/>
+      <c r="J38" s="19" t="inlineStr">
+        <is>
+          <t>완료.</t>
+        </is>
       </c>
       <c r="K38" s="20" t="inlineStr"/>
     </row>
@@ -3171,8 +3241,10 @@
       <c r="I39" s="11" t="n">
         <v/>
       </c>
-      <c r="J39" s="19" t="n">
-        <v/>
+      <c r="J39" s="19" t="inlineStr">
+        <is>
+          <t>완료.</t>
+        </is>
       </c>
       <c r="K39" s="20" t="inlineStr"/>
     </row>
@@ -3218,8 +3290,10 @@
           <t>1~05 입고요청</t>
         </is>
       </c>
-      <c r="J40" s="19" t="n">
-        <v/>
+      <c r="J40" s="19" t="inlineStr">
+        <is>
+          <t>완료.</t>
+        </is>
       </c>
       <c r="K40" s="20" t="inlineStr"/>
     </row>
@@ -3262,8 +3336,10 @@
       <c r="I41" s="11" t="n">
         <v/>
       </c>
-      <c r="J41" s="19" t="n">
-        <v/>
+      <c r="J41" s="19" t="inlineStr">
+        <is>
+          <t>완료.</t>
+        </is>
       </c>
       <c r="K41" s="20" t="inlineStr"/>
     </row>
@@ -3304,8 +3380,10 @@
       <c r="I42" s="11" t="n">
         <v/>
       </c>
-      <c r="J42" s="19" t="n">
-        <v/>
+      <c r="J42" s="19" t="inlineStr">
+        <is>
+          <t>완료.</t>
+        </is>
       </c>
       <c r="K42" s="20" t="inlineStr"/>
     </row>
@@ -3350,8 +3428,10 @@
       <c r="I43" s="11" t="n">
         <v/>
       </c>
-      <c r="J43" s="19" t="n">
-        <v/>
+      <c r="J43" s="19" t="inlineStr">
+        <is>
+          <t>완료.</t>
+        </is>
       </c>
       <c r="K43" s="20" t="inlineStr"/>
     </row>
@@ -3392,8 +3472,10 @@
       <c r="I44" s="11" t="n">
         <v/>
       </c>
-      <c r="J44" s="19" t="n">
-        <v/>
+      <c r="J44" s="19" t="inlineStr">
+        <is>
+          <t>완료.</t>
+        </is>
       </c>
       <c r="K44" s="20" t="inlineStr"/>
     </row>
@@ -3436,8 +3518,10 @@
           <t>1~08 입고요청</t>
         </is>
       </c>
-      <c r="J45" s="19" t="n">
-        <v/>
+      <c r="J45" s="19" t="inlineStr">
+        <is>
+          <t>완료.</t>
+        </is>
       </c>
       <c r="K45" s="20" t="inlineStr"/>
     </row>
@@ -3478,8 +3562,10 @@
       <c r="I46" s="11" t="n">
         <v/>
       </c>
-      <c r="J46" s="19" t="n">
-        <v/>
+      <c r="J46" s="19" t="inlineStr">
+        <is>
+          <t>완료.</t>
+        </is>
       </c>
       <c r="K46" s="20" t="inlineStr"/>
     </row>
@@ -3520,8 +3606,10 @@
       <c r="I47" s="11" t="n">
         <v/>
       </c>
-      <c r="J47" s="19" t="n">
-        <v/>
+      <c r="J47" s="19" t="inlineStr">
+        <is>
+          <t>완료.</t>
+        </is>
       </c>
       <c r="K47" s="20" t="inlineStr"/>
     </row>
@@ -3562,8 +3650,10 @@
       <c r="I48" s="11" t="n">
         <v/>
       </c>
-      <c r="J48" s="19" t="n">
-        <v/>
+      <c r="J48" s="19" t="inlineStr">
+        <is>
+          <t>완료.</t>
+        </is>
       </c>
       <c r="K48" s="20" t="inlineStr"/>
     </row>
@@ -3605,8 +3695,10 @@
       <c r="I49" s="11" t="n">
         <v/>
       </c>
-      <c r="J49" s="19" t="n">
-        <v/>
+      <c r="J49" s="19" t="inlineStr">
+        <is>
+          <t>완료.</t>
+        </is>
       </c>
       <c r="K49" s="20" t="inlineStr"/>
     </row>
@@ -3649,8 +3741,10 @@
       <c r="I50" s="11" t="n">
         <v/>
       </c>
-      <c r="J50" s="19" t="n">
-        <v/>
+      <c r="J50" s="19" t="inlineStr">
+        <is>
+          <t>완료.</t>
+        </is>
       </c>
       <c r="K50" s="20" t="inlineStr"/>
     </row>
@@ -3691,8 +3785,10 @@
       <c r="I51" s="11" t="n">
         <v/>
       </c>
-      <c r="J51" s="19" t="n">
-        <v/>
+      <c r="J51" s="19" t="inlineStr">
+        <is>
+          <t>완료.</t>
+        </is>
       </c>
       <c r="K51" s="20" t="inlineStr"/>
     </row>
@@ -3733,8 +3829,10 @@
       <c r="I52" s="11" t="n">
         <v/>
       </c>
-      <c r="J52" s="19" t="n">
-        <v/>
+      <c r="J52" s="19" t="inlineStr">
+        <is>
+          <t>완료.</t>
+        </is>
       </c>
       <c r="K52" s="20" t="inlineStr"/>
     </row>
@@ -3775,8 +3873,10 @@
       <c r="I53" s="11" t="n">
         <v/>
       </c>
-      <c r="J53" s="19" t="n">
-        <v/>
+      <c r="J53" s="19" t="inlineStr">
+        <is>
+          <t>완료.</t>
+        </is>
       </c>
       <c r="K53" s="20" t="inlineStr"/>
     </row>
@@ -3823,8 +3923,10 @@
       <c r="I54" s="11" t="n">
         <v/>
       </c>
-      <c r="J54" s="19" t="n">
-        <v/>
+      <c r="J54" s="19" t="inlineStr">
+        <is>
+          <t>완료.</t>
+        </is>
       </c>
       <c r="K54" s="20" t="inlineStr">
         <is>
@@ -3871,8 +3973,10 @@
       <c r="I55" s="11" t="n">
         <v/>
       </c>
-      <c r="J55" s="19" t="n">
-        <v/>
+      <c r="J55" s="19" t="inlineStr">
+        <is>
+          <t>완료.</t>
+        </is>
       </c>
       <c r="K55" s="20" t="inlineStr">
         <is>
@@ -3917,8 +4021,10 @@
       <c r="I56" s="11" t="n">
         <v/>
       </c>
-      <c r="J56" s="19" t="n">
-        <v/>
+      <c r="J56" s="19" t="inlineStr">
+        <is>
+          <t>완료.</t>
+        </is>
       </c>
       <c r="K56" s="20" t="inlineStr"/>
     </row>
@@ -3960,8 +4066,10 @@
       <c r="I57" s="11" t="n">
         <v/>
       </c>
-      <c r="J57" s="19" t="n">
-        <v/>
+      <c r="J57" s="19" t="inlineStr">
+        <is>
+          <t>완료.</t>
+        </is>
       </c>
       <c r="K57" s="20" t="inlineStr">
         <is>
@@ -4006,8 +4114,10 @@
       <c r="I58" s="11" t="n">
         <v/>
       </c>
-      <c r="J58" s="19" t="n">
-        <v/>
+      <c r="J58" s="19" t="inlineStr">
+        <is>
+          <t>완료.</t>
+        </is>
       </c>
       <c r="K58" s="20" t="inlineStr"/>
     </row>
@@ -4050,8 +4160,10 @@
       <c r="I59" s="11" t="n">
         <v/>
       </c>
-      <c r="J59" s="19" t="n">
-        <v/>
+      <c r="J59" s="19" t="inlineStr">
+        <is>
+          <t>완료.</t>
+        </is>
       </c>
       <c r="K59" s="20" t="inlineStr">
         <is>
@@ -4096,8 +4208,10 @@
       <c r="I60" s="11" t="n">
         <v/>
       </c>
-      <c r="J60" s="19" t="n">
-        <v/>
+      <c r="J60" s="19" t="inlineStr">
+        <is>
+          <t>완료.</t>
+        </is>
       </c>
       <c r="K60" s="20" t="inlineStr"/>
     </row>
@@ -4138,8 +4252,10 @@
       <c r="I61" s="11" t="n">
         <v/>
       </c>
-      <c r="J61" s="19" t="n">
-        <v/>
+      <c r="J61" s="19" t="inlineStr">
+        <is>
+          <t>완료.</t>
+        </is>
       </c>
       <c r="K61" s="20" t="inlineStr"/>
     </row>
@@ -4182,8 +4298,10 @@
           <t>1~27 입고요청</t>
         </is>
       </c>
-      <c r="J62" s="19" t="n">
-        <v/>
+      <c r="J62" s="19" t="inlineStr">
+        <is>
+          <t>완료.</t>
+        </is>
       </c>
       <c r="K62" s="20" t="inlineStr">
         <is>
@@ -4229,8 +4347,10 @@
       <c r="I63" s="11" t="n">
         <v/>
       </c>
-      <c r="J63" s="19" t="n">
-        <v/>
+      <c r="J63" s="19" t="inlineStr">
+        <is>
+          <t>완료.</t>
+        </is>
       </c>
       <c r="K63" s="20" t="inlineStr">
         <is>
@@ -4275,8 +4395,10 @@
       <c r="I64" s="11" t="n">
         <v/>
       </c>
-      <c r="J64" s="19" t="n">
-        <v/>
+      <c r="J64" s="19" t="inlineStr">
+        <is>
+          <t>완료.</t>
+        </is>
       </c>
       <c r="K64" s="20" t="inlineStr">
         <is>
@@ -4324,8 +4446,10 @@
       <c r="I65" s="11" t="n">
         <v/>
       </c>
-      <c r="J65" s="19" t="n">
-        <v/>
+      <c r="J65" s="19" t="inlineStr">
+        <is>
+          <t>완료.</t>
+        </is>
       </c>
       <c r="K65" s="20" t="inlineStr">
         <is>
@@ -4372,8 +4496,10 @@
       <c r="I66" s="11" t="n">
         <v/>
       </c>
-      <c r="J66" s="19" t="n">
-        <v/>
+      <c r="J66" s="19" t="inlineStr">
+        <is>
+          <t>완료.</t>
+        </is>
       </c>
       <c r="K66" s="20" t="inlineStr">
         <is>
@@ -4419,8 +4545,10 @@
       <c r="I67" s="11" t="n">
         <v/>
       </c>
-      <c r="J67" s="19" t="n">
-        <v/>
+      <c r="J67" s="19" t="inlineStr">
+        <is>
+          <t>완료.</t>
+        </is>
       </c>
       <c r="K67" s="20" t="inlineStr">
         <is>
@@ -4467,8 +4595,10 @@
       <c r="I68" s="11" t="n">
         <v/>
       </c>
-      <c r="J68" s="19" t="n">
-        <v/>
+      <c r="J68" s="19" t="inlineStr">
+        <is>
+          <t>완료.</t>
+        </is>
       </c>
       <c r="K68" s="20" t="inlineStr"/>
     </row>
@@ -4513,8 +4643,10 @@
       <c r="I69" s="11" t="n">
         <v/>
       </c>
-      <c r="J69" s="19" t="n">
-        <v/>
+      <c r="J69" s="19" t="inlineStr">
+        <is>
+          <t>완료.</t>
+        </is>
       </c>
       <c r="K69" s="20" t="inlineStr"/>
     </row>
@@ -4556,8 +4688,10 @@
       <c r="I70" s="11" t="n">
         <v/>
       </c>
-      <c r="J70" s="19" t="n">
-        <v/>
+      <c r="J70" s="19" t="inlineStr">
+        <is>
+          <t>완료.</t>
+        </is>
       </c>
       <c r="K70" s="20" t="inlineStr">
         <is>
@@ -4604,8 +4738,10 @@
       <c r="I71" s="11" t="n">
         <v/>
       </c>
-      <c r="J71" s="19" t="n">
-        <v/>
+      <c r="J71" s="19" t="inlineStr">
+        <is>
+          <t>완료.</t>
+        </is>
       </c>
       <c r="K71" s="20" t="inlineStr">
         <is>
@@ -4656,8 +4792,10 @@
       <c r="I72" s="11" t="n">
         <v/>
       </c>
-      <c r="J72" s="19" t="n">
-        <v/>
+      <c r="J72" s="19" t="inlineStr">
+        <is>
+          <t>완료.</t>
+        </is>
       </c>
       <c r="K72" s="20" t="inlineStr">
         <is>
@@ -4706,8 +4844,10 @@
       <c r="I73" s="11" t="n">
         <v/>
       </c>
-      <c r="J73" s="19" t="n">
-        <v/>
+      <c r="J73" s="19" t="inlineStr">
+        <is>
+          <t>완료.</t>
+        </is>
       </c>
       <c r="K73" s="20" t="inlineStr">
         <is>
@@ -4752,8 +4892,10 @@
       <c r="I74" s="11" t="n">
         <v/>
       </c>
-      <c r="J74" s="19" t="n">
-        <v/>
+      <c r="J74" s="19" t="inlineStr">
+        <is>
+          <t>완료.</t>
+        </is>
       </c>
       <c r="K74" s="20" t="inlineStr"/>
     </row>
@@ -4794,8 +4936,10 @@
       <c r="I75" s="11" t="n">
         <v/>
       </c>
-      <c r="J75" s="19" t="n">
-        <v/>
+      <c r="J75" s="19" t="inlineStr">
+        <is>
+          <t>완료.</t>
+        </is>
       </c>
       <c r="K75" s="20" t="inlineStr">
         <is>
@@ -4840,8 +4984,10 @@
       <c r="I76" s="11" t="n">
         <v/>
       </c>
-      <c r="J76" s="19" t="n">
-        <v/>
+      <c r="J76" s="19" t="inlineStr">
+        <is>
+          <t>완료.</t>
+        </is>
       </c>
       <c r="K76" s="20" t="inlineStr">
         <is>
@@ -4886,8 +5032,10 @@
       <c r="I77" s="11" t="n">
         <v/>
       </c>
-      <c r="J77" s="19" t="n">
-        <v/>
+      <c r="J77" s="19" t="inlineStr">
+        <is>
+          <t>완료.</t>
+        </is>
       </c>
       <c r="K77" s="20" t="inlineStr">
         <is>
@@ -4936,8 +5084,10 @@
       <c r="I78" s="11" t="n">
         <v/>
       </c>
-      <c r="J78" s="19" t="n">
-        <v/>
+      <c r="J78" s="19" t="inlineStr">
+        <is>
+          <t>완료.</t>
+        </is>
       </c>
       <c r="K78" s="20" t="inlineStr">
         <is>
@@ -4983,8 +5133,10 @@
       <c r="I79" s="11" t="n">
         <v/>
       </c>
-      <c r="J79" s="19" t="n">
-        <v/>
+      <c r="J79" s="19" t="inlineStr">
+        <is>
+          <t>완료.</t>
+        </is>
       </c>
       <c r="K79" s="20" t="inlineStr"/>
     </row>
@@ -5025,8 +5177,10 @@
       <c r="I80" s="11" t="n">
         <v/>
       </c>
-      <c r="J80" s="19" t="n">
-        <v/>
+      <c r="J80" s="19" t="inlineStr">
+        <is>
+          <t>완료.</t>
+        </is>
       </c>
       <c r="K80" s="20" t="inlineStr">
         <is>
@@ -5180,8 +5334,10 @@
       <c r="I83" s="11" t="n">
         <v/>
       </c>
-      <c r="J83" s="19" t="n">
-        <v/>
+      <c r="J83" s="19" t="inlineStr">
+        <is>
+          <t>완료.</t>
+        </is>
       </c>
       <c r="K83" s="20" t="inlineStr"/>
     </row>
@@ -5223,8 +5379,10 @@
       <c r="I84" s="11" t="n">
         <v/>
       </c>
-      <c r="J84" s="19" t="n">
-        <v/>
+      <c r="J84" s="19" t="inlineStr">
+        <is>
+          <t>완료.</t>
+        </is>
       </c>
       <c r="K84" s="20" t="inlineStr"/>
     </row>

--- a/data/ECN/ECN_STN_Master(SLH1).xlsx
+++ b/data/ECN/ECN_STN_Master(SLH1).xlsx
@@ -1429,7 +1429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:K84"/>
+  <dimension ref="A2:K85"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.796875" defaultRowHeight="17.4"/>
   <cols>
     <col width="1.69921875" customWidth="1" style="16" min="1" max="1"/>
@@ -1770,9 +1770,7 @@
         </is>
       </c>
       <c r="H8" s="2" t="n"/>
-      <c r="I8" s="11" t="n">
-        <v/>
-      </c>
+      <c r="I8" s="11" t="n"/>
       <c r="J8" s="19" t="inlineStr">
         <is>
           <t>완료.</t>
@@ -1818,9 +1816,7 @@
 -현재 SLH1 PC는 USB 3.0 PORT 로 구성되어있음</t>
         </is>
       </c>
-      <c r="I9" s="11" t="n">
-        <v/>
-      </c>
+      <c r="I9" s="11" t="n"/>
       <c r="J9" s="19" t="inlineStr">
         <is>
           <t>완료.</t>
@@ -1910,9 +1906,7 @@
           <t>-RD Tray Bending 개선, Rail 갈림현상 개선 -LPCAMM Tray Rail 갈림현상 개선</t>
         </is>
       </c>
-      <c r="I11" s="11" t="n">
-        <v/>
-      </c>
+      <c r="I11" s="11" t="n"/>
       <c r="J11" s="19" t="inlineStr">
         <is>
           <t>완료.</t>
@@ -1955,9 +1949,7 @@
           <t>SLH1 RD 최종 Insert(Latch 제거) 및 T-tray Bom Update</t>
         </is>
       </c>
-      <c r="I12" s="11" t="n">
-        <v/>
-      </c>
+      <c r="I12" s="11" t="n"/>
       <c r="J12" s="19" t="inlineStr">
         <is>
           <t>완료.</t>
@@ -2095,9 +2087,7 @@
           <t>SLH1 RD 최종 INSERT 수량 정정(1ea&gt;16ea)</t>
         </is>
       </c>
-      <c r="I15" s="11" t="n">
-        <v/>
-      </c>
+      <c r="I15" s="11" t="n"/>
       <c r="J15" s="19" t="inlineStr">
         <is>
           <t>완료.</t>
@@ -2139,9 +2129,7 @@
           <t>플러팅 기능 불가로 인한 가공 추가(선진행 요청)</t>
         </is>
       </c>
-      <c r="I16" s="11" t="n">
-        <v/>
-      </c>
+      <c r="I16" s="11" t="n"/>
       <c r="J16" s="19" t="inlineStr">
         <is>
           <t>완료.</t>
@@ -2290,9 +2278,7 @@
  - LM과 조립 불가로 조립 기준 변경</t>
         </is>
       </c>
-      <c r="I19" s="11" t="n">
-        <v/>
-      </c>
+      <c r="I19" s="11" t="n"/>
       <c r="J19" s="19" t="inlineStr">
         <is>
           <t>완료.</t>
@@ -2441,9 +2427,7 @@
 -도면 업데이트 및 부적합 사항 수정</t>
         </is>
       </c>
-      <c r="I22" s="11" t="n">
-        <v/>
-      </c>
+      <c r="I22" s="11" t="n"/>
       <c r="J22" s="19" t="inlineStr">
         <is>
           <t>완료.</t>
@@ -2489,9 +2473,7 @@
 -신규 STOPPER 발주</t>
         </is>
       </c>
-      <c r="I23" s="11" t="n">
-        <v/>
-      </c>
+      <c r="I23" s="11" t="n"/>
       <c r="J23" s="19" t="inlineStr">
         <is>
           <t>완료.</t>
@@ -2535,9 +2517,7 @@
 -Cover의 풀림 방지를 위한 너트 추가</t>
         </is>
       </c>
-      <c r="I24" s="11" t="n">
-        <v/>
-      </c>
+      <c r="I24" s="11" t="n"/>
       <c r="J24" s="19" t="inlineStr">
         <is>
           <t>완료.</t>
@@ -2582,9 +2562,7 @@
 -크기 및 성능 동일 하며 CE 및 UL 인증 확인 완료.</t>
         </is>
       </c>
-      <c r="I25" s="11" t="n">
-        <v/>
-      </c>
+      <c r="I25" s="11" t="n"/>
       <c r="J25" s="19" t="inlineStr">
         <is>
           <t>완료.</t>
@@ -2629,9 +2607,7 @@
 -1호기 때 조립기준과 달라져 배선 방향 변경으로 길이 변경하여 포설 필요</t>
         </is>
       </c>
-      <c r="I26" s="11" t="n">
-        <v/>
-      </c>
+      <c r="I26" s="11" t="n"/>
       <c r="J26" s="19" t="inlineStr">
         <is>
           <t>완료.</t>
@@ -2682,9 +2658,7 @@
  - 간섭 미사용 구매품 폐기</t>
         </is>
       </c>
-      <c r="I27" s="11" t="n">
-        <v/>
-      </c>
+      <c r="I27" s="11" t="n"/>
       <c r="J27" s="19" t="inlineStr">
         <is>
           <t>완료.</t>
@@ -2727,9 +2701,7 @@
 -제조팀 요청 공압 선 정리를 위한 홀 추가</t>
         </is>
       </c>
-      <c r="I28" s="11" t="n">
-        <v/>
-      </c>
+      <c r="I28" s="11" t="n"/>
       <c r="J28" s="19" t="inlineStr">
         <is>
           <t>완료.</t>
@@ -2771,9 +2743,7 @@
           <t>잦은 파손으로 인한 재질 및 후처리 변경</t>
         </is>
       </c>
-      <c r="I29" s="11" t="n">
-        <v/>
-      </c>
+      <c r="I29" s="11" t="n"/>
       <c r="J29" s="19" t="inlineStr">
         <is>
           <t>완료.</t>
@@ -2815,9 +2785,7 @@
           <t>고객사 요청 가공품 재질 및 후처리 변경</t>
         </is>
       </c>
-      <c r="I30" s="11" t="n">
-        <v/>
-      </c>
+      <c r="I30" s="11" t="n"/>
       <c r="J30" s="19" t="inlineStr">
         <is>
           <t>완료.</t>
@@ -2863,9 +2831,7 @@
 -치수 누락으로 인한 도면 UPDATE (현품수정)</t>
         </is>
       </c>
-      <c r="I31" s="11" t="n">
-        <v/>
-      </c>
+      <c r="I31" s="11" t="n"/>
       <c r="J31" s="19" t="inlineStr">
         <is>
           <t>완료.</t>
@@ -2907,9 +2873,7 @@
           <t>FITTING 연결부 크기 미일치로 인해 FITTING변경</t>
         </is>
       </c>
-      <c r="I32" s="11" t="n">
-        <v/>
-      </c>
+      <c r="I32" s="11" t="n"/>
       <c r="J32" s="19" t="inlineStr">
         <is>
           <t>완료.</t>
@@ -2954,9 +2918,7 @@
 -모니터 회전의 어려움으로 인한 샤프트 길이 변경</t>
         </is>
       </c>
-      <c r="I33" s="11" t="n">
-        <v/>
-      </c>
+      <c r="I33" s="11" t="n"/>
       <c r="J33" s="19" t="inlineStr">
         <is>
           <t>완료.</t>
@@ -2999,9 +2961,7 @@
 -전장판 떨림 방지 개선</t>
         </is>
       </c>
-      <c r="I34" s="11" t="n">
-        <v/>
-      </c>
+      <c r="I34" s="11" t="n"/>
       <c r="J34" s="19" t="inlineStr">
         <is>
           <t>완료.</t>
@@ -3050,9 +3010,7 @@
 -D컷 가공 추가</t>
         </is>
       </c>
-      <c r="I35" s="11" t="n">
-        <v/>
-      </c>
+      <c r="I35" s="11" t="n"/>
       <c r="J35" s="19" t="inlineStr">
         <is>
           <t>완료.</t>
@@ -3098,9 +3056,7 @@
 -제조팀 요청 솔블록 추가</t>
         </is>
       </c>
-      <c r="I36" s="11" t="n">
-        <v/>
-      </c>
+      <c r="I36" s="11" t="n"/>
       <c r="J36" s="19" t="inlineStr">
         <is>
           <t>완료.</t>
@@ -3145,9 +3101,7 @@
 -탭 위치 불량으로 인한 탭 추가</t>
         </is>
       </c>
-      <c r="I37" s="11" t="n">
-        <v/>
-      </c>
+      <c r="I37" s="11" t="n"/>
       <c r="J37" s="19" t="inlineStr">
         <is>
           <t>완료.</t>
@@ -3191,9 +3145,7 @@
 -STACKER STOPPER 흐트러짐 개선 건(1호기 테스트 완료)</t>
         </is>
       </c>
-      <c r="I38" s="11" t="n">
-        <v/>
-      </c>
+      <c r="I38" s="11" t="n"/>
       <c r="J38" s="19" t="inlineStr">
         <is>
           <t>완료.</t>
@@ -3238,9 +3190,7 @@
 -RAN CABLE 수량 누락</t>
         </is>
       </c>
-      <c r="I39" s="11" t="n">
-        <v/>
-      </c>
+      <c r="I39" s="11" t="n"/>
       <c r="J39" s="19" t="inlineStr">
         <is>
           <t>완료.</t>
@@ -3333,9 +3283,7 @@
 -전장팀 요청 버튼 조작을 위한 REAR MONITER COVER의 여닫이 COVER 추가</t>
         </is>
       </c>
-      <c r="I41" s="11" t="n">
-        <v/>
-      </c>
+      <c r="I41" s="11" t="n"/>
       <c r="J41" s="19" t="inlineStr">
         <is>
           <t>완료.</t>
@@ -3377,9 +3325,7 @@
           <t xml:space="preserve"> -SLH1 SOCAMM 전용 T-TRAY,MASK, PRECISER 등록 및 2호기 적용파트 발주 건(업체 JIG 지정 요청)</t>
         </is>
       </c>
-      <c r="I42" s="11" t="n">
-        <v/>
-      </c>
+      <c r="I42" s="11" t="n"/>
       <c r="J42" s="19" t="inlineStr">
         <is>
           <t>완료.</t>
@@ -3425,9 +3371,7 @@
 ㄴ항목 11,13 수량 삭제 12,14 수량 변경 및 추가분 발주(SLH1-PP-251230-11 발주분 외 추가 발주) </t>
         </is>
       </c>
-      <c r="I43" s="11" t="n">
-        <v/>
-      </c>
+      <c r="I43" s="11" t="n"/>
       <c r="J43" s="19" t="inlineStr">
         <is>
           <t>완료.</t>
@@ -3469,9 +3413,7 @@
           <t>도면 높이 치수 공차 추가 BOM UPDATE</t>
         </is>
       </c>
-      <c r="I44" s="11" t="n">
-        <v/>
-      </c>
+      <c r="I44" s="11" t="n"/>
       <c r="J44" s="19" t="inlineStr">
         <is>
           <t>완료.</t>
@@ -3559,9 +3501,7 @@
           <t>제조팀 요청 마운트 탭 추가</t>
         </is>
       </c>
-      <c r="I46" s="11" t="n">
-        <v/>
-      </c>
+      <c r="I46" s="11" t="n"/>
       <c r="J46" s="19" t="inlineStr">
         <is>
           <t>완료.</t>
@@ -3603,9 +3543,7 @@
           <t>VISION BRK 변경</t>
         </is>
       </c>
-      <c r="I47" s="11" t="n">
-        <v/>
-      </c>
+      <c r="I47" s="11" t="n"/>
       <c r="J47" s="19" t="inlineStr">
         <is>
           <t>완료.</t>
@@ -3647,9 +3585,7 @@
           <t>FRAME 고정용 ANCHOR BRK 추가</t>
         </is>
       </c>
-      <c r="I48" s="11" t="n">
-        <v/>
-      </c>
+      <c r="I48" s="11" t="n"/>
       <c r="J48" s="19" t="inlineStr">
         <is>
           <t>완료.</t>
@@ -3692,9 +3628,7 @@
 -EMS 황색 명판 삭제 요청(고객사 요청)</t>
         </is>
       </c>
-      <c r="I49" s="11" t="n">
-        <v/>
-      </c>
+      <c r="I49" s="11" t="n"/>
       <c r="J49" s="19" t="inlineStr">
         <is>
           <t>완료.</t>
@@ -3738,9 +3672,7 @@
 -AF-BM 으로 변경하여 적용 예정</t>
         </is>
       </c>
-      <c r="I50" s="11" t="n">
-        <v/>
-      </c>
+      <c r="I50" s="11" t="n"/>
       <c r="J50" s="19" t="inlineStr">
         <is>
           <t>완료.</t>
@@ -3782,9 +3714,7 @@
           <t>SLH1 SOCAMM INSC0-IB-06-0 : AD32CM INSERT 부품과 공용 사용/기존 도면 참조</t>
         </is>
       </c>
-      <c r="I51" s="11" t="n">
-        <v/>
-      </c>
+      <c r="I51" s="11" t="n"/>
       <c r="J51" s="19" t="inlineStr">
         <is>
           <t>완료.</t>
@@ -3826,9 +3756,7 @@
           <t>LED 설치 BRK 추가</t>
         </is>
       </c>
-      <c r="I52" s="11" t="n">
-        <v/>
-      </c>
+      <c r="I52" s="11" t="n"/>
       <c r="J52" s="19" t="inlineStr">
         <is>
           <t>완료.</t>
@@ -3870,9 +3798,7 @@
           <t>TRAY GUIDE BLOCK 길이 다르게 수정하여 TEST 진행</t>
         </is>
       </c>
-      <c r="I53" s="11" t="n">
-        <v/>
-      </c>
+      <c r="I53" s="11" t="n"/>
       <c r="J53" s="19" t="inlineStr">
         <is>
           <t>완료.</t>
@@ -3920,9 +3846,7 @@
 -신규 블록 추가로 인한 홀 추가</t>
         </is>
       </c>
-      <c r="I54" s="11" t="n">
-        <v/>
-      </c>
+      <c r="I54" s="11" t="n"/>
       <c r="J54" s="19" t="inlineStr">
         <is>
           <t>완료.</t>
@@ -3970,9 +3894,7 @@
 -BUSH BLOCK TAP 양면 가공 추가</t>
         </is>
       </c>
-      <c r="I55" s="11" t="n">
-        <v/>
-      </c>
+      <c r="I55" s="11" t="n"/>
       <c r="J55" s="19" t="inlineStr">
         <is>
           <t>완료.</t>
@@ -4018,9 +3940,7 @@
           <t>장비 제작 간 케이블 하네스 불합리 및 누락 케이블 추가 업데이트 및 구매</t>
         </is>
       </c>
-      <c r="I56" s="11" t="n">
-        <v/>
-      </c>
+      <c r="I56" s="11" t="n"/>
       <c r="J56" s="19" t="inlineStr">
         <is>
           <t>완료.</t>
@@ -4063,9 +3983,7 @@
 -제조팀 요청 간섭 및 조립 편의성을 위한 홀 타입 변경</t>
         </is>
       </c>
-      <c r="I57" s="11" t="n">
-        <v/>
-      </c>
+      <c r="I57" s="11" t="n"/>
       <c r="J57" s="19" t="inlineStr">
         <is>
           <t>완료.</t>
@@ -4111,9 +4029,7 @@
           <t>SOCAMM HAND VISION BRK 변경으로 인한 설계 변경</t>
         </is>
       </c>
-      <c r="I58" s="11" t="n">
-        <v/>
-      </c>
+      <c r="I58" s="11" t="n"/>
       <c r="J58" s="19" t="inlineStr">
         <is>
           <t>완료.</t>
@@ -4157,9 +4073,7 @@
 -신규 브라켓 추가로 인한 블록 TAP 추가</t>
         </is>
       </c>
-      <c r="I59" s="11" t="n">
-        <v/>
-      </c>
+      <c r="I59" s="11" t="n"/>
       <c r="J59" s="19" t="inlineStr">
         <is>
           <t>완료.</t>
@@ -4205,9 +4119,7 @@
           <t>장비 제작 간 케이블 하네스 불합리 및 누락 케이블 추가 업데이트</t>
         </is>
       </c>
-      <c r="I60" s="11" t="n">
-        <v/>
-      </c>
+      <c r="I60" s="11" t="n"/>
       <c r="J60" s="19" t="inlineStr">
         <is>
           <t>완료.</t>
@@ -4249,9 +4161,7 @@
           <t>장비 제작 간 케이블 하네스 불합리 및 누락 케이블 추가 업데이트</t>
         </is>
       </c>
-      <c r="I61" s="11" t="n">
-        <v/>
-      </c>
+      <c r="I61" s="11" t="n"/>
       <c r="J61" s="19" t="inlineStr">
         <is>
           <t>완료.</t>
@@ -4344,9 +4254,7 @@
 -ALIGN SHAFT 위치 조절 불가로 인한 블록 형상 변경</t>
         </is>
       </c>
-      <c r="I63" s="11" t="n">
-        <v/>
-      </c>
+      <c r="I63" s="11" t="n"/>
       <c r="J63" s="19" t="inlineStr">
         <is>
           <t>완료.</t>
@@ -4392,9 +4300,7 @@
           <t>고객사 요구사항에 대응되는 PAD로 변경(마크리스 특수코팅 추가)</t>
         </is>
       </c>
-      <c r="I64" s="11" t="n">
-        <v/>
-      </c>
+      <c r="I64" s="11" t="n"/>
       <c r="J64" s="19" t="inlineStr">
         <is>
           <t>완료.</t>
@@ -4443,9 +4349,7 @@
 -고객사 요청 재질 변경</t>
         </is>
       </c>
-      <c r="I65" s="11" t="n">
-        <v/>
-      </c>
+      <c r="I65" s="11" t="n"/>
       <c r="J65" s="19" t="inlineStr">
         <is>
           <t>완료.</t>
@@ -4493,9 +4397,7 @@
 -케이블과 간섭으로 인한 가공 추가</t>
         </is>
       </c>
-      <c r="I66" s="11" t="n">
-        <v/>
-      </c>
+      <c r="I66" s="11" t="n"/>
       <c r="J66" s="19" t="inlineStr">
         <is>
           <t>완료.</t>
@@ -4542,9 +4444,7 @@
 -TRAY 진입 불가로 인한 가공품 두께 변경</t>
         </is>
       </c>
-      <c r="I67" s="11" t="n">
-        <v/>
-      </c>
+      <c r="I67" s="11" t="n"/>
       <c r="J67" s="19" t="inlineStr">
         <is>
           <t>완료.</t>
@@ -4592,9 +4492,7 @@
 -하위 파트 REV 변경에 따른 REV 변경, 조립 위치 변경</t>
         </is>
       </c>
-      <c r="I68" s="11" t="n">
-        <v/>
-      </c>
+      <c r="I68" s="11" t="n"/>
       <c r="J68" s="19" t="inlineStr">
         <is>
           <t>완료.</t>
@@ -4640,9 +4538,7 @@
 -SPRING 결합 위치 변경 및 OPEN 각도 조정을 위한 형상 변경</t>
         </is>
       </c>
-      <c r="I69" s="11" t="n">
-        <v/>
-      </c>
+      <c r="I69" s="11" t="n"/>
       <c r="J69" s="19" t="inlineStr">
         <is>
           <t>완료.</t>
@@ -4685,9 +4581,7 @@
 -가공업체 요청 라운드 값 변경, 표면 저항값 삭제</t>
         </is>
       </c>
-      <c r="I70" s="11" t="n">
-        <v/>
-      </c>
+      <c r="I70" s="11" t="n"/>
       <c r="J70" s="19" t="inlineStr">
         <is>
           <t>완료.</t>
@@ -4735,9 +4629,7 @@
 -STACKER MANUAL PORT 롤러 간섭으로 인한 가공 추가</t>
         </is>
       </c>
-      <c r="I71" s="11" t="n">
-        <v/>
-      </c>
+      <c r="I71" s="11" t="n"/>
       <c r="J71" s="19" t="inlineStr">
         <is>
           <t>완료.</t>
@@ -4789,9 +4681,7 @@
 -구매팀 요청 CCTV 세트화 해제로 인한 추가 발주</t>
         </is>
       </c>
-      <c r="I72" s="11" t="n">
-        <v/>
-      </c>
+      <c r="I72" s="11" t="n"/>
       <c r="J72" s="19" t="inlineStr">
         <is>
           <t>완료.</t>
@@ -4841,9 +4731,7 @@
 -SHAFT 사이의 틈이 좁아 휨 이슈로 인한 가공 추가</t>
         </is>
       </c>
-      <c r="I73" s="11" t="n">
-        <v/>
-      </c>
+      <c r="I73" s="11" t="n"/>
       <c r="J73" s="19" t="inlineStr">
         <is>
           <t>완료.</t>
@@ -4889,9 +4777,7 @@
           <t>BOM 수량 MISS 건 BOM UPDATE</t>
         </is>
       </c>
-      <c r="I74" s="11" t="n">
-        <v/>
-      </c>
+      <c r="I74" s="11" t="n"/>
       <c r="J74" s="19" t="inlineStr">
         <is>
           <t>완료.</t>
@@ -4933,9 +4819,7 @@
           <t>고객사 요청 판넬 모서리 보호대 추가</t>
         </is>
       </c>
-      <c r="I75" s="11" t="n">
-        <v/>
-      </c>
+      <c r="I75" s="11" t="n"/>
       <c r="J75" s="19" t="inlineStr">
         <is>
           <t>완료.</t>
@@ -4981,9 +4865,7 @@
           <t>CCTV 브라켓 신규 추가</t>
         </is>
       </c>
-      <c r="I76" s="11" t="n">
-        <v/>
-      </c>
+      <c r="I76" s="11" t="n"/>
       <c r="J76" s="19" t="inlineStr">
         <is>
           <t>완료.</t>
@@ -5029,9 +4911,7 @@
           <t>장비제작 간 케이블 하네스 불합리 및 누락 케이블 추가 업데이트</t>
         </is>
       </c>
-      <c r="I77" s="11" t="n">
-        <v/>
-      </c>
+      <c r="I77" s="11" t="n"/>
       <c r="J77" s="19" t="inlineStr">
         <is>
           <t>완료.</t>
@@ -5081,9 +4961,7 @@
 -신규 브라켓 추가로 인한 기존 브라켓 및 ROLLER 4EA 폐기</t>
         </is>
       </c>
-      <c r="I78" s="11" t="n">
-        <v/>
-      </c>
+      <c r="I78" s="11" t="n"/>
       <c r="J78" s="19" t="inlineStr">
         <is>
           <t>완료.</t>
@@ -5130,9 +5008,7 @@
 -설계 MISS로 인한 변경 진행(긴급, 고객 검수 다음주 진행)</t>
         </is>
       </c>
-      <c r="I79" s="11" t="n">
-        <v/>
-      </c>
+      <c r="I79" s="11" t="n"/>
       <c r="J79" s="19" t="inlineStr">
         <is>
           <t>완료.</t>
@@ -5174,9 +5050,7 @@
           <t>고객사 요청 SOCAMM HAND GRIP의 공압을 최소로 가져가기 위한 브라켓 설계 변경 및 SPACER, AIR FILTER 추가</t>
         </is>
       </c>
-      <c r="I80" s="11" t="n">
-        <v/>
-      </c>
+      <c r="I80" s="11" t="n"/>
       <c r="J80" s="19" t="inlineStr">
         <is>
           <t>완료.</t>
@@ -5225,9 +5099,7 @@
 -SOCAMM PRECISER CONVERSION 체크 브러캣 추가</t>
         </is>
       </c>
-      <c r="I81" s="11" t="n">
-        <v/>
-      </c>
+      <c r="I81" s="11" t="n"/>
       <c r="J81" s="19" t="inlineStr">
         <is>
           <t>완료.</t>
@@ -5279,9 +5151,7 @@
 -SOCAMM STACKER ALIGN SHAFT 처짐으로 인한 BRACKET,LM GUIDE 추가</t>
         </is>
       </c>
-      <c r="I82" s="11" t="n">
-        <v/>
-      </c>
+      <c r="I82" s="11" t="n"/>
       <c r="J82" s="19" t="inlineStr">
         <is>
           <t>횡전개 완료.</t>
@@ -5331,9 +5201,7 @@
 -상위 ASSY 도면 업데이트</t>
         </is>
       </c>
-      <c r="I83" s="11" t="n">
-        <v/>
-      </c>
+      <c r="I83" s="11" t="n"/>
       <c r="J83" s="19" t="inlineStr">
         <is>
           <t>완료.</t>
@@ -5376,15 +5244,62 @@
 -STACKER REJECK BOTTOM 컨베이어 STOP을 위한 센서 홀 없음</t>
         </is>
       </c>
-      <c r="I84" s="11" t="n">
-        <v/>
-      </c>
+      <c r="I84" s="11" t="n"/>
       <c r="J84" s="19" t="inlineStr">
         <is>
           <t>완료.</t>
         </is>
       </c>
       <c r="K84" s="20" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr"/>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>기구설계팀</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>손희주</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SLH1 </t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>SLH1-PP-260506-01</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>STACKER REJECT ALIGN GUIDE 기능 불가로 인한 개선 건</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>-STACKER REJECT ALIGN GUIDE BRACKET 사이의 폭이 C-TRAY의 폭 보다 넓어 매번 같은 위치로 투입 불가  / -STACKER REJECT ALIGN GUIDE BRACKET의 SIZE 축소, 두 파트로 나누어 조절 포인트 추가</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>대기</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>\\192.168.0.100\500 생산\550 국내CS\ECN&amp;STN\SLH1-PP-260506-01.pdf</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
